--- a/virginia-election-2025/virginia-election-results-2025.xlsx
+++ b/virginia-election-2025/virginia-election-results-2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\jordanraddick.com\virginia-election-2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raddick/Documents/GitHub/election-cartograms/virginia-election-2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072D0F0B-1ECF-40B3-A968-0DF4E1D28EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA9EA91-7883-6B4A-A8E6-0BDE69EF59E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59205" yWindow="1830" windowWidth="21600" windowHeight="13725" xr2:uid="{0E396475-42DD-AE41-A480-59BA8D260A07}"/>
+    <workbookView xWindow="6120" yWindow="12160" windowWidth="28800" windowHeight="16140" xr2:uid="{0E396475-42DD-AE41-A480-59BA8D260A07}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -1028,18 +1028,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1055,7 +1049,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
@@ -1071,8 +1065,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1408,16 +1400,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{106E5172-1224-614C-89AD-2F64C2710462}">
-  <dimension ref="A1:AC206"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E206"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="17.125" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" customWidth="1"/>
     <col min="3" max="3" width="15.5" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>310</v>
       </c>
@@ -1434,2529 +1426,2097 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="str">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="str">
+        <f>'Wikipedia table'!A43</f>
+        <v>Fairfax County</v>
+      </c>
+      <c r="B2" s="3">
+        <f>'Wikipedia table'!B43</f>
+        <v>116053</v>
+      </c>
+      <c r="C2" s="3">
+        <f>'Wikipedia table'!D43</f>
+        <v>329977</v>
+      </c>
+      <c r="D2">
+        <f>'Wikipedia table'!F43</f>
+        <v>1222</v>
+      </c>
+      <c r="E2" s="3">
+        <f>SUM(B2:D2)</f>
+        <v>447252</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="str">
+        <f>'Wikipedia table'!A30</f>
+        <v>Chesterfield</v>
+      </c>
+      <c r="B3" s="3">
+        <f>'Wikipedia table'!B30</f>
+        <v>70021</v>
+      </c>
+      <c r="C3" s="3">
+        <f>'Wikipedia table'!D30</f>
+        <v>100595</v>
+      </c>
+      <c r="D3">
+        <f>'Wikipedia table'!F30</f>
+        <v>294</v>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM(B3:D3)</f>
+        <v>170910</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="str">
+        <f>'Wikipedia table'!A128</f>
+        <v>Virginia Beach</v>
+      </c>
+      <c r="B4" s="3">
+        <f>'Wikipedia table'!B128</f>
+        <v>75013</v>
+      </c>
+      <c r="C4" s="3">
+        <f>'Wikipedia table'!D128</f>
+        <v>94339</v>
+      </c>
+      <c r="D4">
+        <f>'Wikipedia table'!F128</f>
+        <v>269</v>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM(B4:D4)</f>
+        <v>169621</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="str">
+        <f>'Wikipedia table'!A75</f>
+        <v>Loudoun</v>
+      </c>
+      <c r="B5" s="3">
+        <f>'Wikipedia table'!B75</f>
+        <v>59278</v>
+      </c>
+      <c r="C5" s="3">
+        <f>'Wikipedia table'!D75</f>
+        <v>108594</v>
+      </c>
+      <c r="D5">
+        <f>'Wikipedia table'!F75</f>
+        <v>444</v>
+      </c>
+      <c r="E5" s="3">
+        <f>SUM(B5:D5)</f>
+        <v>168316</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="str">
+        <f>'Wikipedia table'!A105</f>
+        <v>Prince William</v>
+      </c>
+      <c r="B6" s="3">
+        <f>'Wikipedia table'!B105</f>
+        <v>54309</v>
+      </c>
+      <c r="C6" s="3">
+        <f>'Wikipedia table'!D105</f>
+        <v>111198</v>
+      </c>
+      <c r="D6">
+        <f>'Wikipedia table'!F105</f>
+        <v>381</v>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM(B6:D6)</f>
+        <v>165888</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="str">
+        <f>'Wikipedia table'!A63</f>
+        <v>Henrico</v>
+      </c>
+      <c r="B7" s="3">
+        <f>'Wikipedia table'!B63</f>
+        <v>45627</v>
+      </c>
+      <c r="C7" s="3">
+        <f>'Wikipedia table'!D63</f>
+        <v>103559</v>
+      </c>
+      <c r="D7">
+        <f>'Wikipedia table'!F63</f>
+        <v>260</v>
+      </c>
+      <c r="E7" s="3">
+        <f>SUM(B7:D7)</f>
+        <v>149446</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="str">
+        <f>'Wikipedia table'!A12</f>
+        <v>Arlington</v>
+      </c>
+      <c r="B8" s="3">
+        <f>'Wikipedia table'!B12</f>
+        <v>15929</v>
+      </c>
+      <c r="C8" s="3">
+        <f>'Wikipedia table'!D12</f>
+        <v>83657</v>
+      </c>
+      <c r="D8">
+        <f>'Wikipedia table'!F12</f>
+        <v>235</v>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM(B8:D8)</f>
+        <v>99821</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="str">
+        <f>'Wikipedia table'!A29</f>
+        <v>Chesapeake</v>
+      </c>
+      <c r="B9" s="3">
+        <f>'Wikipedia table'!B29</f>
+        <v>42147</v>
+      </c>
+      <c r="C9" s="3">
+        <f>'Wikipedia table'!D29</f>
+        <v>53971</v>
+      </c>
+      <c r="D9">
+        <f>'Wikipedia table'!F29</f>
+        <v>164</v>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM(B9:D9)</f>
+        <v>96282</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="str">
+        <f>'Wikipedia table'!A109</f>
+        <v>Richmond City</v>
+      </c>
+      <c r="B10" s="3">
+        <f>'Wikipedia table'!B109</f>
+        <v>11883</v>
+      </c>
+      <c r="C10" s="3">
+        <f>'Wikipedia table'!D109</f>
+        <v>79019</v>
+      </c>
+      <c r="D10">
+        <f>'Wikipedia table'!F109</f>
+        <v>212</v>
+      </c>
+      <c r="E10" s="3">
+        <f>SUM(B10:D10)</f>
+        <v>91114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="str">
+        <f>'Wikipedia table'!A90</f>
+        <v>Norfolk</v>
+      </c>
+      <c r="B11" s="3">
+        <f>'Wikipedia table'!B90</f>
+        <v>15509</v>
+      </c>
+      <c r="C11" s="3">
+        <f>'Wikipedia table'!D90</f>
+        <v>48599</v>
+      </c>
+      <c r="D11">
+        <f>'Wikipedia table'!F90</f>
+        <v>111</v>
+      </c>
+      <c r="E11" s="3">
+        <f>SUM(B11:D11)</f>
+        <v>64219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="str">
+        <f>'Wikipedia table'!A122</f>
+        <v>Stafford</v>
+      </c>
+      <c r="B12" s="3">
+        <f>'Wikipedia table'!B122</f>
+        <v>27774</v>
+      </c>
+      <c r="C12" s="3">
+        <f>'Wikipedia table'!D122</f>
+        <v>35327</v>
+      </c>
+      <c r="D12">
+        <f>'Wikipedia table'!F122</f>
+        <v>115</v>
+      </c>
+      <c r="E12" s="3">
+        <f>SUM(B12:D12)</f>
+        <v>63216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="str">
+        <f>'Wikipedia table'!A7</f>
+        <v>Alexandria</v>
+      </c>
+      <c r="B13" s="3">
+        <f>'Wikipedia table'!B7</f>
+        <v>10424</v>
+      </c>
+      <c r="C13" s="3">
+        <f>'Wikipedia table'!D7</f>
+        <v>52230</v>
+      </c>
+      <c r="D13">
+        <f>'Wikipedia table'!F7</f>
+        <v>190</v>
+      </c>
+      <c r="E13" s="3">
+        <f>SUM(B13:D13)</f>
+        <v>62844</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="str">
+        <f>'Wikipedia table'!A61</f>
+        <v>Hanover</v>
+      </c>
+      <c r="B14" s="3">
+        <f>'Wikipedia table'!B61</f>
+        <v>36278</v>
+      </c>
+      <c r="C14" s="3">
+        <f>'Wikipedia table'!D61</f>
+        <v>23994</v>
+      </c>
+      <c r="D14">
+        <f>'Wikipedia table'!F61</f>
+        <v>95</v>
+      </c>
+      <c r="E14" s="3">
+        <f>SUM(B14:D14)</f>
+        <v>60367</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="str">
+        <f>'Wikipedia table'!A121</f>
+        <v>Spotsylvania</v>
+      </c>
+      <c r="B15" s="3">
+        <f>'Wikipedia table'!B121</f>
+        <v>29015</v>
+      </c>
+      <c r="C15" s="3">
+        <f>'Wikipedia table'!D121</f>
+        <v>30748</v>
+      </c>
+      <c r="D15">
+        <f>'Wikipedia table'!F121</f>
+        <v>104</v>
+      </c>
+      <c r="E15" s="3">
+        <f>SUM(B15:D15)</f>
+        <v>59867</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" t="str">
+        <f>'Wikipedia table'!A89</f>
+        <v>Newport News</v>
+      </c>
+      <c r="B16" s="3">
+        <f>'Wikipedia table'!B89</f>
+        <v>17461</v>
+      </c>
+      <c r="C16" s="3">
+        <f>'Wikipedia table'!D89</f>
+        <v>38936</v>
+      </c>
+      <c r="D16">
+        <f>'Wikipedia table'!F89</f>
+        <v>92</v>
+      </c>
+      <c r="E16" s="3">
+        <f>SUM(B16:D16)</f>
+        <v>56489</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="str">
+        <f>'Wikipedia table'!A6</f>
+        <v>Albemarle</v>
+      </c>
+      <c r="B17" s="3">
+        <f>'Wikipedia table'!B6</f>
+        <v>16480</v>
+      </c>
+      <c r="C17" s="3">
+        <f>'Wikipedia table'!D6</f>
+        <v>39322</v>
+      </c>
+      <c r="D17">
+        <f>'Wikipedia table'!F6</f>
+        <v>93</v>
+      </c>
+      <c r="E17" s="3">
+        <f>SUM(B17:D17)</f>
+        <v>55895</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="str">
+        <f>'Wikipedia table'!A60</f>
+        <v>Hampton</v>
+      </c>
+      <c r="B18" s="3">
+        <f>'Wikipedia table'!B60</f>
+        <v>12103</v>
+      </c>
+      <c r="C18" s="3">
+        <f>'Wikipedia table'!D60</f>
+        <v>35129</v>
+      </c>
+      <c r="D18">
+        <f>'Wikipedia table'!F60</f>
+        <v>91</v>
+      </c>
+      <c r="E18" s="3">
+        <f>SUM(B18:D18)</f>
+        <v>47323</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="str">
+        <f>'Wikipedia table'!A112</f>
+        <v>Roanoke County</v>
+      </c>
+      <c r="B19" s="3">
+        <f>'Wikipedia table'!B112</f>
+        <v>24728</v>
+      </c>
+      <c r="C19" s="3">
+        <f>'Wikipedia table'!D112</f>
+        <v>18062</v>
+      </c>
+      <c r="D19">
+        <f>'Wikipedia table'!F112</f>
+        <v>97</v>
+      </c>
+      <c r="E19" s="3">
+        <f>SUM(B19:D19)</f>
+        <v>42887</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="str">
+        <f>'Wikipedia table'!A68</f>
+        <v>James City</v>
+      </c>
+      <c r="B20" s="3">
+        <f>'Wikipedia table'!B68</f>
+        <v>19029</v>
+      </c>
+      <c r="C20" s="3">
+        <f>'Wikipedia table'!D68</f>
+        <v>23603</v>
+      </c>
+      <c r="D20">
+        <f>'Wikipedia table'!F68</f>
+        <v>63</v>
+      </c>
+      <c r="E20" s="3">
+        <f>SUM(B20:D20)</f>
+        <v>42695</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="str">
+        <f>'Wikipedia table'!A124</f>
+        <v>Suffolk</v>
+      </c>
+      <c r="B21" s="3">
+        <f>'Wikipedia table'!B124</f>
+        <v>15935</v>
+      </c>
+      <c r="C21" s="3">
+        <f>'Wikipedia table'!D124</f>
+        <v>25696</v>
+      </c>
+      <c r="D21">
+        <f>'Wikipedia table'!F124</f>
+        <v>80</v>
+      </c>
+      <c r="E21" s="3">
+        <f>SUM(B21:D21)</f>
+        <v>41711</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="str">
+        <f>'Wikipedia table'!A15</f>
+        <v>Bedford</v>
+      </c>
+      <c r="B22" s="3">
+        <f>'Wikipedia table'!B15</f>
+        <v>29166</v>
+      </c>
+      <c r="C22" s="3">
+        <f>'Wikipedia table'!D15</f>
+        <v>10048</v>
+      </c>
+      <c r="D22">
+        <f>'Wikipedia table'!F15</f>
+        <v>57</v>
+      </c>
+      <c r="E22" s="3">
+        <f>SUM(B22:D22)</f>
+        <v>39271</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="str">
+        <f>'Wikipedia table'!A50</f>
+        <v>Frederick</v>
+      </c>
+      <c r="B23" s="3">
+        <f>'Wikipedia table'!B50</f>
+        <v>23130</v>
+      </c>
+      <c r="C23" s="3">
+        <f>'Wikipedia table'!D50</f>
+        <v>15809</v>
+      </c>
+      <c r="D23">
+        <f>'Wikipedia table'!F50</f>
+        <v>51</v>
+      </c>
+      <c r="E23" s="3">
+        <f>SUM(B23:D23)</f>
+        <v>38990</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="str">
+        <f>'Wikipedia table'!A86</f>
+        <v>Montgomery</v>
+      </c>
+      <c r="B24" s="3">
+        <f>'Wikipedia table'!B86</f>
+        <v>15228</v>
+      </c>
+      <c r="C24" s="3">
+        <f>'Wikipedia table'!D86</f>
+        <v>21428</v>
+      </c>
+      <c r="D24">
+        <f>'Wikipedia table'!F86</f>
+        <v>76</v>
+      </c>
+      <c r="E24" s="3">
+        <f>SUM(B24:D24)</f>
+        <v>36732</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="str">
+        <f>'Wikipedia table'!A114</f>
+        <v>Rockingham</v>
+      </c>
+      <c r="B25" s="3">
+        <f>'Wikipedia table'!B114</f>
+        <v>24498</v>
+      </c>
+      <c r="C25" s="3">
+        <f>'Wikipedia table'!D114</f>
+        <v>11622</v>
+      </c>
+      <c r="D25">
+        <f>'Wikipedia table'!F114</f>
+        <v>76</v>
+      </c>
+      <c r="E25" s="3">
+        <f>SUM(B25:D25)</f>
+        <v>36196</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="str">
+        <f>'Wikipedia table'!A45</f>
+        <v>Fauquier</v>
+      </c>
+      <c r="B26" s="3">
+        <f>'Wikipedia table'!B45</f>
+        <v>19894</v>
+      </c>
+      <c r="C26" s="3">
+        <f>'Wikipedia table'!D45</f>
+        <v>14610</v>
+      </c>
+      <c r="D26">
+        <f>'Wikipedia table'!F45</f>
+        <v>62</v>
+      </c>
+      <c r="E26" s="3">
+        <f>SUM(B26:D26)</f>
+        <v>34566</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="str">
+        <f>'Wikipedia table'!A13</f>
+        <v>Augusta</v>
+      </c>
+      <c r="B27" s="3">
+        <f>'Wikipedia table'!B13</f>
+        <v>24612</v>
+      </c>
+      <c r="C27" s="3">
+        <f>'Wikipedia table'!D13</f>
+        <v>9522</v>
+      </c>
+      <c r="D27">
+        <f>'Wikipedia table'!F13</f>
+        <v>60</v>
+      </c>
+      <c r="E27" s="3">
+        <f>SUM(B27:D27)</f>
+        <v>34194</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="str">
+        <f>'Wikipedia table'!A137</f>
+        <v>York</v>
+      </c>
+      <c r="B28" s="3">
+        <f>'Wikipedia table'!B137</f>
+        <v>15684</v>
+      </c>
+      <c r="C28" s="3">
+        <f>'Wikipedia table'!D137</f>
+        <v>15769</v>
+      </c>
+      <c r="D28">
+        <f>'Wikipedia table'!F137</f>
+        <v>47</v>
+      </c>
+      <c r="E28" s="3">
+        <f>SUM(B28:D28)</f>
+        <v>31500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="str">
+        <f>'Wikipedia table'!A101</f>
+        <v>Portsmouth</v>
+      </c>
+      <c r="B29" s="3">
+        <f>'Wikipedia table'!B101</f>
+        <v>8351</v>
+      </c>
+      <c r="C29" s="3">
+        <f>'Wikipedia table'!D101</f>
+        <v>23040</v>
+      </c>
+      <c r="D29">
+        <f>'Wikipedia table'!F101</f>
+        <v>62</v>
+      </c>
+      <c r="E29" s="3">
+        <f>SUM(B29:D29)</f>
+        <v>31453</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="str">
+        <f>'Wikipedia table'!A111</f>
+        <v>Roanoke City</v>
+      </c>
+      <c r="B30" s="3">
+        <f>'Wikipedia table'!B111</f>
+        <v>10153</v>
+      </c>
+      <c r="C30" s="3">
+        <f>'Wikipedia table'!D111</f>
+        <v>20700</v>
+      </c>
+      <c r="D30">
+        <f>'Wikipedia table'!F111</f>
+        <v>83</v>
+      </c>
+      <c r="E30" s="3">
+        <f>SUM(B30:D30)</f>
+        <v>30936</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" t="str">
+        <f>'Wikipedia table'!A78</f>
+        <v>Lynchburg</v>
+      </c>
+      <c r="B31" s="3">
+        <f>'Wikipedia table'!B78</f>
+        <v>13508</v>
+      </c>
+      <c r="C31" s="3">
+        <f>'Wikipedia table'!D78</f>
+        <v>13231</v>
+      </c>
+      <c r="D31">
+        <f>'Wikipedia table'!F78</f>
+        <v>56</v>
+      </c>
+      <c r="E31" s="3">
+        <f>SUM(B31:D31)</f>
+        <v>26795</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="str">
+        <f>'Wikipedia table'!A99</f>
+        <v>Pittsylvania</v>
+      </c>
+      <c r="B32" s="3">
+        <f>'Wikipedia table'!B99</f>
+        <v>17439</v>
+      </c>
+      <c r="C32" s="3">
+        <f>'Wikipedia table'!D99</f>
+        <v>7272</v>
+      </c>
+      <c r="D32">
+        <f>'Wikipedia table'!F99</f>
+        <v>38</v>
+      </c>
+      <c r="E32" s="3">
+        <f>SUM(B32:D32)</f>
+        <v>24749</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" t="str">
+        <f>'Wikipedia table'!A49</f>
+        <v>Franklin County</v>
+      </c>
+      <c r="B33" s="3">
+        <f>'Wikipedia table'!B49</f>
+        <v>16317</v>
+      </c>
+      <c r="C33" s="3">
+        <f>'Wikipedia table'!D49</f>
+        <v>6836</v>
+      </c>
+      <c r="D33">
+        <f>'Wikipedia table'!F49</f>
+        <v>36</v>
+      </c>
+      <c r="E33" s="3">
+        <f>SUM(B33:D33)</f>
+        <v>23189</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
+        <f>'Wikipedia table'!A23</f>
+        <v>Campbell</v>
+      </c>
+      <c r="B34" s="3">
+        <f>'Wikipedia table'!B23</f>
+        <v>16878</v>
+      </c>
+      <c r="C34" s="3">
+        <f>'Wikipedia table'!D23</f>
+        <v>6130</v>
+      </c>
+      <c r="D34">
+        <f>'Wikipedia table'!F23</f>
+        <v>34</v>
+      </c>
+      <c r="E34" s="3">
+        <f>SUM(B34:D34)</f>
+        <v>23042</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" t="str">
+        <f>'Wikipedia table'!A35</f>
+        <v>Culpeper</v>
+      </c>
+      <c r="B35" s="3">
+        <f>'Wikipedia table'!B35</f>
+        <v>12592</v>
+      </c>
+      <c r="C35" s="3">
+        <f>'Wikipedia table'!D35</f>
+        <v>9214</v>
+      </c>
+      <c r="D35">
+        <f>'Wikipedia table'!F35</f>
+        <v>33</v>
+      </c>
+      <c r="E35" s="3">
+        <f>SUM(B35:D35)</f>
+        <v>21839</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" t="str">
+        <f>'Wikipedia table'!A130</f>
+        <v>Washington</v>
+      </c>
+      <c r="B36" s="3">
+        <f>'Wikipedia table'!B130</f>
+        <v>15614</v>
+      </c>
+      <c r="C36" s="3">
+        <f>'Wikipedia table'!D130</f>
+        <v>5382</v>
+      </c>
+      <c r="D36">
+        <f>'Wikipedia table'!F130</f>
+        <v>43</v>
+      </c>
+      <c r="E36" s="3">
+        <f>SUM(B36:D36)</f>
+        <v>21039</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" t="str">
+        <f>'Wikipedia table'!A67</f>
+        <v>Isle of Wight</v>
+      </c>
+      <c r="B37" s="3">
+        <f>'Wikipedia table'!B67</f>
+        <v>10931</v>
+      </c>
+      <c r="C37" s="3">
+        <f>'Wikipedia table'!D67</f>
+        <v>8227</v>
+      </c>
+      <c r="D37">
+        <f>'Wikipedia table'!F67</f>
+        <v>37</v>
+      </c>
+      <c r="E37" s="3">
+        <f>SUM(B37:D37)</f>
+        <v>19195</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" t="str">
+        <f>'Wikipedia table'!A76</f>
+        <v>Louisa</v>
+      </c>
+      <c r="B38" s="3">
+        <f>'Wikipedia table'!B76</f>
+        <v>11279</v>
+      </c>
+      <c r="C38" s="3">
+        <f>'Wikipedia table'!D76</f>
+        <v>7628</v>
+      </c>
+      <c r="D38">
+        <f>'Wikipedia table'!F76</f>
+        <v>44</v>
+      </c>
+      <c r="E38" s="3">
+        <f>SUM(B38:D38)</f>
+        <v>18951</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" t="str">
+        <f>'Wikipedia table'!A28</f>
+        <v>Charlottesville</v>
+      </c>
+      <c r="B39" s="3">
+        <f>'Wikipedia table'!B28</f>
+        <v>2056</v>
+      </c>
+      <c r="C39" s="3">
+        <f>'Wikipedia table'!D28</f>
+        <v>16799</v>
+      </c>
+      <c r="D39">
+        <f>'Wikipedia table'!F28</f>
+        <v>35</v>
+      </c>
+      <c r="E39" s="3">
+        <f>SUM(B39:D39)</f>
+        <v>18890</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" t="str">
+        <f>'Wikipedia table'!A118</f>
+        <v>Shenandoah</v>
+      </c>
+      <c r="B40" s="3">
+        <f>'Wikipedia table'!B118</f>
+        <v>12488</v>
+      </c>
+      <c r="C40" s="3">
+        <f>'Wikipedia table'!D118</f>
+        <v>5698</v>
+      </c>
+      <c r="D40">
+        <f>'Wikipedia table'!F118</f>
+        <v>37</v>
+      </c>
+      <c r="E40" s="3">
+        <f>SUM(B40:D40)</f>
+        <v>18223</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" t="str">
+        <f>'Wikipedia table'!A64</f>
+        <v>Henry</v>
+      </c>
+      <c r="B41" s="3">
+        <f>'Wikipedia table'!B64</f>
+        <v>11150</v>
+      </c>
+      <c r="C41" s="3">
+        <f>'Wikipedia table'!D64</f>
+        <v>6320</v>
+      </c>
+      <c r="D41">
+        <f>'Wikipedia table'!F64</f>
+        <v>30</v>
+      </c>
+      <c r="E41" s="3">
+        <f>SUM(B41:D41)</f>
+        <v>17500</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" t="str">
+        <f>'Wikipedia table'!A54</f>
+        <v>Gloucester</v>
+      </c>
+      <c r="B42" s="3">
+        <f>'Wikipedia table'!B54</f>
+        <v>11399</v>
+      </c>
+      <c r="C42" s="3">
+        <f>'Wikipedia table'!D54</f>
+        <v>5912</v>
+      </c>
+      <c r="D42">
+        <f>'Wikipedia table'!F54</f>
+        <v>30</v>
+      </c>
+      <c r="E42" s="3">
+        <f>SUM(B42:D42)</f>
+        <v>17341</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" t="str">
+        <f>'Wikipedia table'!A95</f>
+        <v>Orange</v>
+      </c>
+      <c r="B43" s="3">
+        <f>'Wikipedia table'!B95</f>
+        <v>9938</v>
+      </c>
+      <c r="C43" s="3">
+        <f>'Wikipedia table'!D95</f>
+        <v>7361</v>
+      </c>
+      <c r="D43">
+        <f>'Wikipedia table'!F95</f>
+        <v>33</v>
+      </c>
+      <c r="E43" s="3">
+        <f>SUM(B43:D43)</f>
+        <v>17332</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" t="str">
+        <f>'Wikipedia table'!A55</f>
+        <v>Goochland</v>
+      </c>
+      <c r="B44" s="3">
+        <f>'Wikipedia table'!B55</f>
+        <v>9726</v>
+      </c>
+      <c r="C44" s="3">
+        <f>'Wikipedia table'!D55</f>
+        <v>7339</v>
+      </c>
+      <c r="D44">
+        <f>'Wikipedia table'!F55</f>
+        <v>24</v>
+      </c>
+      <c r="E44" s="3">
+        <f>SUM(B44:D44)</f>
+        <v>17089</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" t="str">
+        <f>'Wikipedia table'!A102</f>
+        <v>Powhatan</v>
+      </c>
+      <c r="B45" s="3">
+        <f>'Wikipedia table'!B102</f>
+        <v>11862</v>
+      </c>
+      <c r="C45" s="3">
+        <f>'Wikipedia table'!D102</f>
+        <v>5168</v>
+      </c>
+      <c r="D45">
+        <f>'Wikipedia table'!F102</f>
+        <v>21</v>
+      </c>
+      <c r="E45" s="3">
+        <f>SUM(B45:D45)</f>
+        <v>17051</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" t="str">
+        <f>'Wikipedia table'!A17</f>
+        <v>Botetourt</v>
+      </c>
+      <c r="B46" s="3">
+        <f>'Wikipedia table'!B17</f>
+        <v>11820</v>
+      </c>
+      <c r="C46" s="3">
+        <f>'Wikipedia table'!D17</f>
+        <v>4969</v>
+      </c>
+      <c r="D46">
+        <f>'Wikipedia table'!F17</f>
+        <v>32</v>
+      </c>
+      <c r="E46" s="3">
+        <f>SUM(B46:D46)</f>
+        <v>16821</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" t="str">
+        <f>'Wikipedia table'!A129</f>
+        <v>Warren</v>
+      </c>
+      <c r="B47" s="3">
+        <f>'Wikipedia table'!B129</f>
+        <v>10433</v>
+      </c>
+      <c r="C47" s="3">
+        <f>'Wikipedia table'!D129</f>
+        <v>5757</v>
+      </c>
+      <c r="D47">
+        <f>'Wikipedia table'!F129</f>
+        <v>39</v>
+      </c>
+      <c r="E47" s="3">
+        <f>SUM(B47:D47)</f>
+        <v>16229</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" t="str">
+        <f>'Wikipedia table'!A88</f>
+        <v>New Kent</v>
+      </c>
+      <c r="B48" s="3">
+        <f>'Wikipedia table'!B88</f>
+        <v>8804</v>
+      </c>
+      <c r="C48" s="3">
+        <f>'Wikipedia table'!D88</f>
+        <v>5087</v>
+      </c>
+      <c r="D48">
+        <f>'Wikipedia table'!F88</f>
+        <v>22</v>
+      </c>
+      <c r="E48" s="3">
+        <f>SUM(B48:D48)</f>
+        <v>13913</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" t="str">
+        <f>'Wikipedia table'!A104</f>
+        <v>Prince George</v>
+      </c>
+      <c r="B49" s="3">
+        <f>'Wikipedia table'!B104</f>
+        <v>7986</v>
+      </c>
+      <c r="C49" s="3">
+        <f>'Wikipedia table'!D104</f>
+        <v>5707</v>
+      </c>
+      <c r="D49">
+        <f>'Wikipedia table'!F104</f>
+        <v>13</v>
+      </c>
+      <c r="E49" s="3">
+        <f>SUM(B49:D49)</f>
+        <v>13706</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" t="str">
+        <f>'Wikipedia table'!A47</f>
+        <v>Fluvanna</v>
+      </c>
+      <c r="B50" s="3">
+        <f>'Wikipedia table'!B47</f>
+        <v>6718</v>
+      </c>
+      <c r="C50" s="3">
+        <f>'Wikipedia table'!D47</f>
+        <v>6712</v>
+      </c>
+      <c r="D50">
+        <f>'Wikipedia table'!F47</f>
+        <v>19</v>
+      </c>
+      <c r="E50" s="3">
+        <f>SUM(B50:D50)</f>
+        <v>13449</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" t="str">
+        <f>'Wikipedia table'!A24</f>
+        <v>Caroline</v>
+      </c>
+      <c r="B51" s="3">
+        <f>'Wikipedia table'!B24</f>
+        <v>6680</v>
+      </c>
+      <c r="C51" s="3">
+        <f>'Wikipedia table'!D24</f>
+        <v>6733</v>
+      </c>
+      <c r="D51">
+        <f>'Wikipedia table'!F24</f>
+        <v>23</v>
+      </c>
+      <c r="E51" s="3">
+        <f>SUM(B51:D51)</f>
+        <v>13436</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" t="str">
+        <f>'Wikipedia table'!A59</f>
+        <v>Halifax</v>
+      </c>
+      <c r="B52" s="3">
+        <f>'Wikipedia table'!B59</f>
+        <v>8027</v>
+      </c>
+      <c r="C52" s="3">
+        <f>'Wikipedia table'!D59</f>
+        <v>5272</v>
+      </c>
+      <c r="D52">
+        <f>'Wikipedia table'!F59</f>
+        <v>22</v>
+      </c>
+      <c r="E52" s="3">
+        <f>SUM(B52:D52)</f>
+        <v>13321</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" t="str">
+        <f>'Wikipedia table'!A62</f>
+        <v>Harrisonburg</v>
+      </c>
+      <c r="B53" s="3">
+        <f>'Wikipedia table'!B62</f>
+        <v>3654</v>
+      </c>
+      <c r="C53" s="3">
+        <f>'Wikipedia table'!D62</f>
+        <v>9512</v>
+      </c>
+      <c r="D53">
+        <f>'Wikipedia table'!F62</f>
+        <v>23</v>
+      </c>
+      <c r="E53" s="3">
+        <f>SUM(B53:D53)</f>
+        <v>13189</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" t="str">
+        <f>'Wikipedia table'!A10</f>
+        <v>Amherst</v>
+      </c>
+      <c r="B54" s="3">
+        <f>'Wikipedia table'!B10</f>
+        <v>8811</v>
+      </c>
+      <c r="C54" s="3">
+        <f>'Wikipedia table'!D10</f>
+        <v>4294</v>
+      </c>
+      <c r="D54">
+        <f>'Wikipedia table'!F10</f>
+        <v>20</v>
+      </c>
+      <c r="E54" s="3">
+        <f>SUM(B54:D54)</f>
+        <v>13125</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" t="str">
         <f>'Wikipedia table'!A5</f>
         <v>Accomack</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B55" s="3">
         <f>'Wikipedia table'!B5</f>
         <v>7129</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C55" s="3">
         <f>'Wikipedia table'!D5</f>
         <v>5925</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D55">
         <f>'Wikipedia table'!F5</f>
         <v>10</v>
       </c>
-      <c r="E2" s="16">
-        <f>SUM(B2:D2)</f>
+      <c r="E55" s="3">
+        <f>SUM(B55:D55)</f>
         <v>13064</v>
       </c>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
-      <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
-    </row>
-    <row r="3" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="str">
-        <f>'Wikipedia table'!A6</f>
-        <v>Albemarle</v>
-      </c>
-      <c r="B3" s="16">
-        <f>'Wikipedia table'!B6</f>
-        <v>16480</v>
-      </c>
-      <c r="C3" s="16">
-        <f>'Wikipedia table'!D6</f>
-        <v>39322</v>
-      </c>
-      <c r="D3" s="15">
-        <f>'Wikipedia table'!F6</f>
-        <v>93</v>
-      </c>
-      <c r="E3" s="16">
-        <f>SUM(B3:D3)</f>
-        <v>55895</v>
-      </c>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
-      <c r="N3"/>
-      <c r="O3"/>
-      <c r="P3"/>
-      <c r="Q3"/>
-      <c r="R3"/>
-      <c r="S3"/>
-      <c r="T3"/>
-      <c r="U3"/>
-      <c r="V3"/>
-      <c r="W3"/>
-      <c r="X3"/>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3"/>
-      <c r="AB3"/>
-      <c r="AC3"/>
-    </row>
-    <row r="4" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="str">
-        <f>'Wikipedia table'!A7</f>
-        <v>Alexandria</v>
-      </c>
-      <c r="B4" s="16">
-        <f>'Wikipedia table'!B7</f>
-        <v>10424</v>
-      </c>
-      <c r="C4" s="16">
-        <f>'Wikipedia table'!D7</f>
-        <v>52230</v>
-      </c>
-      <c r="D4" s="15">
-        <f>'Wikipedia table'!F7</f>
-        <v>190</v>
-      </c>
-      <c r="E4" s="16">
-        <f>SUM(B4:D4)</f>
-        <v>62844</v>
-      </c>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
-      <c r="L4"/>
-      <c r="M4"/>
-      <c r="N4"/>
-      <c r="O4"/>
-      <c r="P4"/>
-      <c r="Q4"/>
-      <c r="R4"/>
-      <c r="S4"/>
-      <c r="T4"/>
-      <c r="U4"/>
-      <c r="V4"/>
-      <c r="W4"/>
-      <c r="X4"/>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4"/>
-      <c r="AB4"/>
-      <c r="AC4"/>
-    </row>
-    <row r="5" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="str">
-        <f>'Wikipedia table'!A8</f>
-        <v>Alleghany</v>
-      </c>
-      <c r="B5" s="16">
-        <f>'Wikipedia table'!B8</f>
-        <v>4011</v>
-      </c>
-      <c r="C5" s="16">
-        <f>'Wikipedia table'!D8</f>
-        <v>1779</v>
-      </c>
-      <c r="D5" s="15">
-        <f>'Wikipedia table'!F8</f>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" t="str">
+        <f>'Wikipedia table'!A127</f>
+        <v>Tazewell</v>
+      </c>
+      <c r="B56" s="3">
+        <f>'Wikipedia table'!B127</f>
+        <v>10407</v>
+      </c>
+      <c r="C56" s="3">
+        <f>'Wikipedia table'!D127</f>
+        <v>2248</v>
+      </c>
+      <c r="D56">
+        <f>'Wikipedia table'!F127</f>
+        <v>21</v>
+      </c>
+      <c r="E56" s="3">
+        <f>SUM(B56:D56)</f>
+        <v>12676</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" t="str">
+        <f>'Wikipedia table'!A106</f>
+        <v>Pulaski</v>
+      </c>
+      <c r="B57" s="3">
+        <f>'Wikipedia table'!B106</f>
+        <v>8607</v>
+      </c>
+      <c r="C57" s="3">
+        <f>'Wikipedia table'!D106</f>
+        <v>3927</v>
+      </c>
+      <c r="D57">
+        <f>'Wikipedia table'!F106</f>
+        <v>22</v>
+      </c>
+      <c r="E57" s="3">
+        <f>SUM(B57:D57)</f>
+        <v>12556</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" t="str">
+        <f>'Wikipedia table'!A37</f>
+        <v>Danville</v>
+      </c>
+      <c r="B58" s="3">
+        <f>'Wikipedia table'!B37</f>
+        <v>4592</v>
+      </c>
+      <c r="C58" s="3">
+        <f>'Wikipedia table'!D37</f>
+        <v>7678</v>
+      </c>
+      <c r="D58">
+        <f>'Wikipedia table'!F37</f>
+        <v>29</v>
+      </c>
+      <c r="E58" s="3">
+        <f>SUM(B58:D58)</f>
+        <v>12299</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" t="str">
+        <f>'Wikipedia table'!A39</f>
+        <v>Dinwiddie</v>
+      </c>
+      <c r="B59" s="3">
+        <f>'Wikipedia table'!B39</f>
+        <v>7028</v>
+      </c>
+      <c r="C59" s="3">
+        <f>'Wikipedia table'!D39</f>
+        <v>5031</v>
+      </c>
+      <c r="D59">
+        <f>'Wikipedia table'!F39</f>
+        <v>19</v>
+      </c>
+      <c r="E59" s="3">
+        <f>SUM(B59:D59)</f>
+        <v>12078</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" t="str">
+        <f>'Wikipedia table'!A84</f>
+        <v>Mecklenburg</v>
+      </c>
+      <c r="B60" s="3">
+        <f>'Wikipedia table'!B84</f>
+        <v>7151</v>
+      </c>
+      <c r="C60" s="3">
+        <f>'Wikipedia table'!D84</f>
+        <v>4657</v>
+      </c>
+      <c r="D60">
+        <f>'Wikipedia table'!F84</f>
         <v>11</v>
       </c>
-      <c r="E5" s="16">
-        <f>SUM(B5:D5)</f>
-        <v>5801</v>
-      </c>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5"/>
-      <c r="L5"/>
-      <c r="M5"/>
-      <c r="N5"/>
-      <c r="O5"/>
-      <c r="P5"/>
-      <c r="Q5"/>
-      <c r="R5"/>
-      <c r="S5"/>
-      <c r="T5"/>
-      <c r="U5"/>
-      <c r="V5"/>
-      <c r="W5"/>
-      <c r="X5"/>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5"/>
-      <c r="AB5"/>
-      <c r="AC5"/>
-    </row>
-    <row r="6" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="str">
+      <c r="E60" s="3">
+        <f>SUM(B60:D60)</f>
+        <v>11819</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" t="str">
+        <f>'Wikipedia table'!A80</f>
+        <v>Manassas</v>
+      </c>
+      <c r="B61" s="3">
+        <f>'Wikipedia table'!B80</f>
+        <v>4036</v>
+      </c>
+      <c r="C61" s="3">
+        <f>'Wikipedia table'!D80</f>
+        <v>7671</v>
+      </c>
+      <c r="D61">
+        <f>'Wikipedia table'!F80</f>
+        <v>18</v>
+      </c>
+      <c r="E61" s="3">
+        <f>SUM(B61:D61)</f>
+        <v>11725</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" t="str">
+        <f>'Wikipedia table'!A70</f>
+        <v>King George</v>
+      </c>
+      <c r="B62" s="3">
+        <f>'Wikipedia table'!B70</f>
+        <v>6909</v>
+      </c>
+      <c r="C62" s="3">
+        <f>'Wikipedia table'!D70</f>
+        <v>4716</v>
+      </c>
+      <c r="D62">
+        <f>'Wikipedia table'!F70</f>
+        <v>20</v>
+      </c>
+      <c r="E62" s="3">
+        <f>SUM(B62:D62)</f>
+        <v>11645</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" t="str">
+        <f>'Wikipedia table'!A25</f>
+        <v>Carroll</v>
+      </c>
+      <c r="B63" s="3">
+        <f>'Wikipedia table'!B25</f>
+        <v>8889</v>
+      </c>
+      <c r="C63" s="3">
+        <f>'Wikipedia table'!D25</f>
+        <v>2433</v>
+      </c>
+      <c r="D63">
+        <f>'Wikipedia table'!F25</f>
+        <v>26</v>
+      </c>
+      <c r="E63" s="3">
+        <f>SUM(B63:D63)</f>
+        <v>11348</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" t="str">
+        <f>'Wikipedia table'!A135</f>
+        <v>Wise</v>
+      </c>
+      <c r="B64" s="3">
+        <f>'Wikipedia table'!B135</f>
+        <v>8744</v>
+      </c>
+      <c r="C64" s="3">
+        <f>'Wikipedia table'!D135</f>
+        <v>2281</v>
+      </c>
+      <c r="D64">
+        <f>'Wikipedia table'!F135</f>
+        <v>22</v>
+      </c>
+      <c r="E64" s="3">
+        <f>SUM(B64:D64)</f>
+        <v>11047</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" t="str">
+        <f>'Wikipedia table'!A136</f>
+        <v>Wythe</v>
+      </c>
+      <c r="B65" s="3">
+        <f>'Wikipedia table'!B136</f>
+        <v>8426</v>
+      </c>
+      <c r="C65" s="3">
+        <f>'Wikipedia table'!D136</f>
+        <v>2594</v>
+      </c>
+      <c r="D65">
+        <f>'Wikipedia table'!F136</f>
+        <v>24</v>
+      </c>
+      <c r="E65" s="3">
+        <f>SUM(B65:D65)</f>
+        <v>11044</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" t="str">
+        <f>'Wikipedia table'!A123</f>
+        <v>Staunton</v>
+      </c>
+      <c r="B66" s="3">
+        <f>'Wikipedia table'!B123</f>
+        <v>4236</v>
+      </c>
+      <c r="C66" s="3">
+        <f>'Wikipedia table'!D123</f>
+        <v>6580</v>
+      </c>
+      <c r="D66">
+        <f>'Wikipedia table'!F123</f>
+        <v>18</v>
+      </c>
+      <c r="E66" s="3">
+        <f>SUM(B66:D66)</f>
+        <v>10834</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" t="str">
+        <f>'Wikipedia table'!A51</f>
+        <v>Fredericksburg</v>
+      </c>
+      <c r="B67" s="3">
+        <f>'Wikipedia table'!B51</f>
+        <v>2943</v>
+      </c>
+      <c r="C67" s="3">
+        <f>'Wikipedia table'!D51</f>
+        <v>7561</v>
+      </c>
+      <c r="D67">
+        <f>'Wikipedia table'!F51</f>
+        <v>33</v>
+      </c>
+      <c r="E67" s="3">
+        <f>SUM(B67:D67)</f>
+        <v>10537</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" t="str">
+        <f>'Wikipedia table'!A42</f>
+        <v>Fairfax City</v>
+      </c>
+      <c r="B68" s="3">
+        <f>'Wikipedia table'!B42</f>
+        <v>2847</v>
+      </c>
+      <c r="C68" s="3">
+        <f>'Wikipedia table'!D42</f>
+        <v>7552</v>
+      </c>
+      <c r="D68">
+        <f>'Wikipedia table'!F42</f>
+        <v>36</v>
+      </c>
+      <c r="E68" s="3">
+        <f>SUM(B68:D68)</f>
+        <v>10435</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" t="str">
+        <f>'Wikipedia table'!A113</f>
+        <v>Rockbridge</v>
+      </c>
+      <c r="B69" s="3">
+        <f>'Wikipedia table'!B113</f>
+        <v>6599</v>
+      </c>
+      <c r="C69" s="3">
+        <f>'Wikipedia table'!D113</f>
+        <v>3557</v>
+      </c>
+      <c r="D69">
+        <f>'Wikipedia table'!F113</f>
+        <v>7</v>
+      </c>
+      <c r="E69" s="3">
+        <f>SUM(B69:D69)</f>
+        <v>10163</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" t="str">
+        <f>'Wikipedia table'!A119</f>
+        <v>Smyth</v>
+      </c>
+      <c r="B70" s="3">
+        <f>'Wikipedia table'!B119</f>
+        <v>7712</v>
+      </c>
+      <c r="C70" s="3">
+        <f>'Wikipedia table'!D119</f>
+        <v>2298</v>
+      </c>
+      <c r="D70">
+        <f>'Wikipedia table'!F119</f>
+        <v>18</v>
+      </c>
+      <c r="E70" s="3">
+        <f>SUM(B70:D70)</f>
+        <v>10028</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" t="str">
+        <f>'Wikipedia table'!A98</f>
+        <v>Petersburg</v>
+      </c>
+      <c r="B71" s="3">
+        <f>'Wikipedia table'!B98</f>
+        <v>1124</v>
+      </c>
+      <c r="C71" s="3">
+        <f>'Wikipedia table'!D98</f>
+        <v>8811</v>
+      </c>
+      <c r="D71">
+        <f>'Wikipedia table'!F98</f>
+        <v>25</v>
+      </c>
+      <c r="E71" s="3">
+        <f>SUM(B71:D71)</f>
+        <v>9960</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" t="str">
+        <f>'Wikipedia table'!A57</f>
+        <v>Greene</v>
+      </c>
+      <c r="B72" s="3">
+        <f>'Wikipedia table'!B57</f>
+        <v>5458</v>
+      </c>
+      <c r="C72" s="3">
+        <f>'Wikipedia table'!D57</f>
+        <v>4036</v>
+      </c>
+      <c r="D72">
+        <f>'Wikipedia table'!F57</f>
+        <v>16</v>
+      </c>
+      <c r="E72" s="3">
+        <f>SUM(B72:D72)</f>
+        <v>9510</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" t="str">
+        <f>'Wikipedia table'!A116</f>
+        <v>Salem</v>
+      </c>
+      <c r="B73" s="3">
+        <f>'Wikipedia table'!B116</f>
+        <v>5282</v>
+      </c>
+      <c r="C73" s="3">
+        <f>'Wikipedia table'!D116</f>
+        <v>4150</v>
+      </c>
+      <c r="D73">
+        <f>'Wikipedia table'!F116</f>
+        <v>32</v>
+      </c>
+      <c r="E73" s="3">
+        <f>SUM(B73:D73)</f>
+        <v>9464</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" t="str">
+        <f>'Wikipedia table'!A96</f>
+        <v>Page</v>
+      </c>
+      <c r="B74" s="3">
+        <f>'Wikipedia table'!B96</f>
+        <v>6940</v>
+      </c>
+      <c r="C74" s="3">
+        <f>'Wikipedia table'!D96</f>
+        <v>2365</v>
+      </c>
+      <c r="D74">
+        <f>'Wikipedia table'!F96</f>
+        <v>24</v>
+      </c>
+      <c r="E74" s="3">
+        <f>SUM(B74:D74)</f>
+        <v>9329</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" t="str">
+        <f>'Wikipedia table'!A71</f>
+        <v>King William</v>
+      </c>
+      <c r="B75" s="3">
+        <f>'Wikipedia table'!B71</f>
+        <v>6033</v>
+      </c>
+      <c r="C75" s="3">
+        <f>'Wikipedia table'!D71</f>
+        <v>3020</v>
+      </c>
+      <c r="D75">
+        <f>'Wikipedia table'!F71</f>
+        <v>11</v>
+      </c>
+      <c r="E75" s="3">
+        <f>SUM(B75:D75)</f>
+        <v>9064</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" t="str">
+        <f>'Wikipedia table'!A115</f>
+        <v>Russell</v>
+      </c>
+      <c r="B76" s="3">
+        <f>'Wikipedia table'!B115</f>
+        <v>7268</v>
+      </c>
+      <c r="C76" s="3">
+        <f>'Wikipedia table'!D115</f>
+        <v>1673</v>
+      </c>
+      <c r="D76">
+        <f>'Wikipedia table'!F115</f>
+        <v>17</v>
+      </c>
+      <c r="E76" s="3">
+        <f>SUM(B76:D76)</f>
+        <v>8958</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" t="str">
+        <f>'Wikipedia table'!A134</f>
+        <v>Winchester</v>
+      </c>
+      <c r="B77" s="3">
+        <f>'Wikipedia table'!B134</f>
+        <v>3485</v>
+      </c>
+      <c r="C77" s="3">
+        <f>'Wikipedia table'!D134</f>
+        <v>5318</v>
+      </c>
+      <c r="D77">
+        <f>'Wikipedia table'!F134</f>
+        <v>16</v>
+      </c>
+      <c r="E77" s="3">
+        <f>SUM(B77:D77)</f>
+        <v>8819</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" t="str">
+        <f>'Wikipedia table'!A131</f>
+        <v>Waynesboro</v>
+      </c>
+      <c r="B78" s="3">
+        <f>'Wikipedia table'!B131</f>
+        <v>4037</v>
+      </c>
+      <c r="C78" s="3">
+        <f>'Wikipedia table'!D131</f>
+        <v>4459</v>
+      </c>
+      <c r="D78">
+        <f>'Wikipedia table'!F131</f>
+        <v>11</v>
+      </c>
+      <c r="E78" s="3">
+        <f>SUM(B78:D78)</f>
+        <v>8507</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" t="str">
+        <f>'Wikipedia table'!A132</f>
+        <v>Westmoreland</v>
+      </c>
+      <c r="B79" s="3">
+        <f>'Wikipedia table'!B132</f>
+        <v>4396</v>
+      </c>
+      <c r="C79" s="3">
+        <f>'Wikipedia table'!D132</f>
+        <v>3733</v>
+      </c>
+      <c r="D79">
+        <f>'Wikipedia table'!F132</f>
+        <v>8</v>
+      </c>
+      <c r="E79" s="3">
+        <f>SUM(B79:D79)</f>
+        <v>8137</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" t="str">
+        <f>'Wikipedia table'!A87</f>
+        <v>Nelson</v>
+      </c>
+      <c r="B80" s="3">
+        <f>'Wikipedia table'!B87</f>
+        <v>3828</v>
+      </c>
+      <c r="C80" s="3">
+        <f>'Wikipedia table'!D87</f>
+        <v>3880</v>
+      </c>
+      <c r="D80">
+        <f>'Wikipedia table'!F87</f>
+        <v>17</v>
+      </c>
+      <c r="E80" s="3">
+        <f>SUM(B80:D80)</f>
+        <v>7725</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" t="str">
+        <f>'Wikipedia table'!A31</f>
+        <v>Clarke</v>
+      </c>
+      <c r="B81" s="3">
+        <f>'Wikipedia table'!B31</f>
+        <v>4222</v>
+      </c>
+      <c r="C81" s="3">
+        <f>'Wikipedia table'!D31</f>
+        <v>3389</v>
+      </c>
+      <c r="D81">
+        <f>'Wikipedia table'!F31</f>
+        <v>18</v>
+      </c>
+      <c r="E81" s="3">
+        <f>SUM(B81:D81)</f>
+        <v>7629</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" t="str">
+        <f>'Wikipedia table'!A44</f>
+        <v>Falls Church</v>
+      </c>
+      <c r="B82" s="3">
+        <f>'Wikipedia table'!B44</f>
+        <v>1181</v>
+      </c>
+      <c r="C82" s="3">
+        <f>'Wikipedia table'!D44</f>
+        <v>6407</v>
+      </c>
+      <c r="D82">
+        <f>'Wikipedia table'!F44</f>
+        <v>12</v>
+      </c>
+      <c r="E82" s="3">
+        <f>SUM(B82:D82)</f>
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" t="str">
+        <f>'Wikipedia table'!A103</f>
+        <v>Prince Edward</v>
+      </c>
+      <c r="B83" s="3">
+        <f>'Wikipedia table'!B103</f>
+        <v>3668</v>
+      </c>
+      <c r="C83" s="3">
+        <f>'Wikipedia table'!D103</f>
+        <v>3767</v>
+      </c>
+      <c r="D83">
+        <f>'Wikipedia table'!F103</f>
+        <v>20</v>
+      </c>
+      <c r="E83" s="3">
+        <f>SUM(B83:D83)</f>
+        <v>7455</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" t="str">
+        <f>'Wikipedia table'!A120</f>
+        <v>Southampton</v>
+      </c>
+      <c r="B84" s="3">
+        <f>'Wikipedia table'!B120</f>
+        <v>4492</v>
+      </c>
+      <c r="C84" s="3">
+        <f>'Wikipedia table'!D120</f>
+        <v>2945</v>
+      </c>
+      <c r="D84">
+        <f>'Wikipedia table'!F120</f>
+        <v>8</v>
+      </c>
+      <c r="E84" s="3">
+        <f>SUM(B84:D84)</f>
+        <v>7445</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" t="str">
+        <f>'Wikipedia table'!A46</f>
+        <v>Floyd</v>
+      </c>
+      <c r="B85" s="3">
+        <f>'Wikipedia table'!B46</f>
+        <v>4806</v>
+      </c>
+      <c r="C85" s="3">
+        <f>'Wikipedia table'!D46</f>
+        <v>2603</v>
+      </c>
+      <c r="D85">
+        <f>'Wikipedia table'!F46</f>
+        <v>16</v>
+      </c>
+      <c r="E85" s="3">
+        <f>SUM(B85:D85)</f>
+        <v>7425</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" t="str">
+        <f>'Wikipedia table'!A11</f>
+        <v>Appomattox</v>
+      </c>
+      <c r="B86" s="3">
+        <f>'Wikipedia table'!B11</f>
+        <v>5609</v>
+      </c>
+      <c r="C86" s="3">
+        <f>'Wikipedia table'!D11</f>
+        <v>1765</v>
+      </c>
+      <c r="D86">
+        <f>'Wikipedia table'!F11</f>
+        <v>12</v>
+      </c>
+      <c r="E86" s="3">
+        <f>SUM(B86:D86)</f>
+        <v>7386</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" t="str">
+        <f>'Wikipedia table'!A117</f>
+        <v>Scott</v>
+      </c>
+      <c r="B87" s="3">
+        <f>'Wikipedia table'!B117</f>
+        <v>6103</v>
+      </c>
+      <c r="C87" s="3">
+        <f>'Wikipedia table'!D117</f>
+        <v>1235</v>
+      </c>
+      <c r="D87">
+        <f>'Wikipedia table'!F117</f>
+        <v>15</v>
+      </c>
+      <c r="E87" s="3">
+        <f>SUM(B87:D87)</f>
+        <v>7353</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" t="str">
+        <f>'Wikipedia table'!A92</f>
+        <v>Northumberland</v>
+      </c>
+      <c r="B88" s="3">
+        <f>'Wikipedia table'!B92</f>
+        <v>4132</v>
+      </c>
+      <c r="C88" s="3">
+        <f>'Wikipedia table'!D92</f>
+        <v>2685</v>
+      </c>
+      <c r="D88">
+        <f>'Wikipedia table'!F92</f>
+        <v>16</v>
+      </c>
+      <c r="E88" s="3">
+        <f>SUM(B88:D88)</f>
+        <v>6833</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" t="str">
+        <f>'Wikipedia table'!A53</f>
+        <v>Giles</v>
+      </c>
+      <c r="B89" s="3">
+        <f>'Wikipedia table'!B53</f>
+        <v>4983</v>
+      </c>
+      <c r="C89" s="3">
+        <f>'Wikipedia table'!D53</f>
+        <v>1782</v>
+      </c>
+      <c r="D89">
+        <f>'Wikipedia table'!F53</f>
+        <v>16</v>
+      </c>
+      <c r="E89" s="3">
+        <f>SUM(B89:D89)</f>
+        <v>6781</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" t="str">
+        <f>'Wikipedia table'!A133</f>
+        <v>Williamsburg</v>
+      </c>
+      <c r="B90" s="3">
+        <f>'Wikipedia table'!B133</f>
+        <v>1647</v>
+      </c>
+      <c r="C90" s="3">
+        <f>'Wikipedia table'!D133</f>
+        <v>5063</v>
+      </c>
+      <c r="D90">
+        <f>'Wikipedia table'!F133</f>
+        <v>9</v>
+      </c>
+      <c r="E90" s="3">
+        <f>SUM(B90:D90)</f>
+        <v>6719</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" t="str">
+        <f>'Wikipedia table'!A66</f>
+        <v>Hopewell</v>
+      </c>
+      <c r="B91" s="3">
+        <f>'Wikipedia table'!B66</f>
+        <v>2610</v>
+      </c>
+      <c r="C91" s="3">
+        <f>'Wikipedia table'!D66</f>
+        <v>4052</v>
+      </c>
+      <c r="D91">
+        <f>'Wikipedia table'!F66</f>
+        <v>13</v>
+      </c>
+      <c r="E91" s="3">
+        <f>SUM(B91:D91)</f>
+        <v>6675</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" t="str">
+        <f>'Wikipedia table'!A79</f>
+        <v>Madison</v>
+      </c>
+      <c r="B92" s="3">
+        <f>'Wikipedia table'!B79</f>
+        <v>4259</v>
+      </c>
+      <c r="C92" s="3">
+        <f>'Wikipedia table'!D79</f>
+        <v>2386</v>
+      </c>
+      <c r="D92">
+        <f>'Wikipedia table'!F79</f>
+        <v>9</v>
+      </c>
+      <c r="E92" s="3">
+        <f>SUM(B92:D92)</f>
+        <v>6654</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" t="str">
+        <f>'Wikipedia table'!A97</f>
+        <v>Patrick</v>
+      </c>
+      <c r="B93" s="3">
+        <f>'Wikipedia table'!B97</f>
+        <v>5119</v>
+      </c>
+      <c r="C93" s="3">
+        <f>'Wikipedia table'!D97</f>
+        <v>1488</v>
+      </c>
+      <c r="D93">
+        <f>'Wikipedia table'!F97</f>
+        <v>5</v>
+      </c>
+      <c r="E93" s="3">
+        <f>SUM(B93:D93)</f>
+        <v>6612</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" t="str">
+        <f>'Wikipedia table'!A32</f>
+        <v>Colonial Heights</v>
+      </c>
+      <c r="B94" s="3">
+        <f>'Wikipedia table'!B32</f>
+        <v>4092</v>
+      </c>
+      <c r="C94" s="3">
+        <f>'Wikipedia table'!D32</f>
+        <v>2474</v>
+      </c>
+      <c r="D94">
+        <f>'Wikipedia table'!F32</f>
+        <v>21</v>
+      </c>
+      <c r="E94" s="3">
+        <f>SUM(B94:D94)</f>
+        <v>6587</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" t="str">
+        <f>'Wikipedia table'!A73</f>
+        <v>Lee</v>
+      </c>
+      <c r="B95" s="3">
+        <f>'Wikipedia table'!B73</f>
+        <v>5439</v>
+      </c>
+      <c r="C95" s="3">
+        <f>'Wikipedia table'!D73</f>
+        <v>1019</v>
+      </c>
+      <c r="D95">
+        <f>'Wikipedia table'!F73</f>
+        <v>7</v>
+      </c>
+      <c r="E95" s="3">
+        <f>SUM(B95:D95)</f>
+        <v>6465</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" t="str">
         <f>'Wikipedia table'!A9</f>
         <v>Amelia</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B96" s="3">
         <f>'Wikipedia table'!B9</f>
         <v>4521</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C96" s="3">
         <f>'Wikipedia table'!D9</f>
         <v>1831</v>
       </c>
-      <c r="D6">
+      <c r="D96">
         <f>'Wikipedia table'!F9</f>
         <v>8</v>
       </c>
-      <c r="E6" s="3">
-        <f>SUM(B6:D6)</f>
-        <v>6360</v>
-      </c>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
-      <c r="L6"/>
-      <c r="M6"/>
-      <c r="N6"/>
-      <c r="O6"/>
-      <c r="P6"/>
-      <c r="Q6"/>
-      <c r="R6"/>
-      <c r="S6"/>
-      <c r="T6"/>
-      <c r="U6"/>
-      <c r="V6"/>
-      <c r="W6"/>
-      <c r="X6"/>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6"/>
-      <c r="AB6"/>
-      <c r="AC6"/>
-    </row>
-    <row r="7" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="str">
-        <f>'Wikipedia table'!A10</f>
-        <v>Amherst</v>
-      </c>
-      <c r="B7" s="3">
-        <f>'Wikipedia table'!B10</f>
-        <v>8811</v>
-      </c>
-      <c r="C7" s="3">
-        <f>'Wikipedia table'!D10</f>
-        <v>4294</v>
-      </c>
-      <c r="D7">
-        <f>'Wikipedia table'!F10</f>
-        <v>20</v>
-      </c>
-      <c r="E7" s="3">
-        <f>SUM(B7:D7)</f>
-        <v>13125</v>
-      </c>
-      <c r="F7"/>
-      <c r="G7"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
-      <c r="L7"/>
-      <c r="M7"/>
-      <c r="N7"/>
-      <c r="O7"/>
-      <c r="P7"/>
-      <c r="Q7"/>
-      <c r="R7"/>
-      <c r="S7"/>
-      <c r="T7"/>
-      <c r="U7"/>
-      <c r="V7"/>
-      <c r="W7"/>
-      <c r="X7"/>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7"/>
-      <c r="AB7"/>
-      <c r="AC7"/>
-    </row>
-    <row r="8" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="str">
-        <f>'Wikipedia table'!A11</f>
-        <v>Appomattox</v>
-      </c>
-      <c r="B8" s="3">
-        <f>'Wikipedia table'!B11</f>
-        <v>5609</v>
-      </c>
-      <c r="C8" s="3">
-        <f>'Wikipedia table'!D11</f>
-        <v>1765</v>
-      </c>
-      <c r="D8">
-        <f>'Wikipedia table'!F11</f>
-        <v>12</v>
-      </c>
-      <c r="E8" s="3">
-        <f>SUM(B8:D8)</f>
-        <v>7386</v>
-      </c>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
-      <c r="L8"/>
-      <c r="M8"/>
-      <c r="N8"/>
-      <c r="O8"/>
-      <c r="P8"/>
-      <c r="Q8"/>
-      <c r="R8"/>
-      <c r="S8"/>
-      <c r="T8"/>
-      <c r="U8"/>
-      <c r="V8"/>
-      <c r="W8"/>
-      <c r="X8"/>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8"/>
-      <c r="AB8"/>
-      <c r="AC8"/>
-    </row>
-    <row r="9" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="str">
-        <f>'Wikipedia table'!A12</f>
-        <v>Arlington</v>
-      </c>
-      <c r="B9" s="16">
-        <f>'Wikipedia table'!B12</f>
-        <v>15929</v>
-      </c>
-      <c r="C9" s="16">
-        <f>'Wikipedia table'!D12</f>
-        <v>83657</v>
-      </c>
-      <c r="D9" s="15">
-        <f>'Wikipedia table'!F12</f>
-        <v>235</v>
-      </c>
-      <c r="E9" s="16">
-        <f>SUM(B9:D9)</f>
-        <v>99821</v>
-      </c>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
-      <c r="N9"/>
-      <c r="O9"/>
-      <c r="P9"/>
-      <c r="Q9"/>
-      <c r="R9"/>
-      <c r="S9"/>
-      <c r="T9"/>
-      <c r="U9"/>
-      <c r="V9"/>
-      <c r="W9"/>
-      <c r="X9"/>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9"/>
-      <c r="AB9"/>
-      <c r="AC9"/>
-    </row>
-    <row r="10" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="str">
-        <f>'Wikipedia table'!A13</f>
-        <v>Augusta</v>
-      </c>
-      <c r="B10" s="3">
-        <f>'Wikipedia table'!B13</f>
-        <v>24612</v>
-      </c>
-      <c r="C10" s="3">
-        <f>'Wikipedia table'!D13</f>
-        <v>9522</v>
-      </c>
-      <c r="D10">
-        <f>'Wikipedia table'!F13</f>
-        <v>60</v>
-      </c>
-      <c r="E10" s="3">
-        <f>SUM(B10:D10)</f>
-        <v>34194</v>
-      </c>
-      <c r="F10"/>
-      <c r="G10"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
-      <c r="K10"/>
-      <c r="L10"/>
-      <c r="M10"/>
-      <c r="N10"/>
-      <c r="O10"/>
-      <c r="P10"/>
-      <c r="Q10"/>
-      <c r="R10"/>
-      <c r="S10"/>
-      <c r="T10"/>
-      <c r="U10"/>
-      <c r="V10"/>
-      <c r="W10"/>
-      <c r="X10"/>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10"/>
-      <c r="AB10"/>
-      <c r="AC10"/>
-    </row>
-    <row r="11" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="str">
-        <f>'Wikipedia table'!A14</f>
-        <v>Bath</v>
-      </c>
-      <c r="B11" s="3">
-        <f>'Wikipedia table'!B14</f>
-        <v>1421</v>
-      </c>
-      <c r="C11" s="3">
-        <f>'Wikipedia table'!D14</f>
-        <v>493</v>
-      </c>
-      <c r="D11">
-        <f>'Wikipedia table'!F14</f>
-        <v>5</v>
-      </c>
-      <c r="E11" s="3">
-        <f>SUM(B11:D11)</f>
-        <v>1919</v>
-      </c>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-      <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11"/>
-      <c r="N11"/>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11"/>
-      <c r="R11"/>
-      <c r="S11"/>
-      <c r="T11"/>
-      <c r="U11"/>
-      <c r="V11"/>
-      <c r="W11"/>
-      <c r="X11"/>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11"/>
-      <c r="AB11"/>
-      <c r="AC11"/>
-    </row>
-    <row r="12" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" t="str">
-        <f>'Wikipedia table'!A15</f>
-        <v>Bedford</v>
-      </c>
-      <c r="B12" s="3">
-        <f>'Wikipedia table'!B15</f>
-        <v>29166</v>
-      </c>
-      <c r="C12" s="3">
-        <f>'Wikipedia table'!D15</f>
-        <v>10048</v>
-      </c>
-      <c r="D12">
-        <f>'Wikipedia table'!F15</f>
-        <v>57</v>
-      </c>
-      <c r="E12" s="3">
-        <f>SUM(B12:D12)</f>
-        <v>39271</v>
-      </c>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
-      <c r="K12"/>
-      <c r="L12"/>
-      <c r="M12"/>
-      <c r="N12"/>
-      <c r="O12"/>
-      <c r="P12"/>
-      <c r="Q12"/>
-      <c r="R12"/>
-      <c r="S12"/>
-      <c r="T12"/>
-      <c r="U12"/>
-      <c r="V12"/>
-      <c r="W12"/>
-      <c r="X12"/>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12"/>
-      <c r="AB12"/>
-      <c r="AC12"/>
-    </row>
-    <row r="13" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="str">
-        <f>'Wikipedia table'!A16</f>
-        <v>Bland</v>
-      </c>
-      <c r="B13" s="3">
-        <f>'Wikipedia table'!B16</f>
-        <v>1974</v>
-      </c>
-      <c r="C13" s="3">
-        <f>'Wikipedia table'!D16</f>
-        <v>441</v>
-      </c>
-      <c r="D13">
-        <f>'Wikipedia table'!F16</f>
-        <v>3</v>
-      </c>
-      <c r="E13" s="3">
-        <f>SUM(B13:D13)</f>
-        <v>2418</v>
-      </c>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13"/>
-      <c r="K13"/>
-      <c r="L13"/>
-      <c r="M13"/>
-      <c r="N13"/>
-      <c r="O13"/>
-      <c r="P13"/>
-      <c r="Q13"/>
-      <c r="R13"/>
-      <c r="S13"/>
-      <c r="T13"/>
-      <c r="U13"/>
-      <c r="V13"/>
-      <c r="W13"/>
-      <c r="X13"/>
-      <c r="Y13"/>
-      <c r="Z13"/>
-      <c r="AA13"/>
-      <c r="AB13"/>
-      <c r="AC13"/>
-    </row>
-    <row r="14" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="str">
-        <f>'Wikipedia table'!A17</f>
-        <v>Botetourt</v>
-      </c>
-      <c r="B14" s="3">
-        <f>'Wikipedia table'!B17</f>
-        <v>11820</v>
-      </c>
-      <c r="C14" s="3">
-        <f>'Wikipedia table'!D17</f>
-        <v>4969</v>
-      </c>
-      <c r="D14">
-        <f>'Wikipedia table'!F17</f>
-        <v>32</v>
-      </c>
-      <c r="E14" s="3">
-        <f>SUM(B14:D14)</f>
-        <v>16821</v>
-      </c>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-      <c r="K14"/>
-      <c r="L14"/>
-      <c r="M14"/>
-      <c r="N14"/>
-      <c r="O14"/>
-      <c r="P14"/>
-      <c r="Q14"/>
-      <c r="R14"/>
-      <c r="S14"/>
-      <c r="T14"/>
-      <c r="U14"/>
-      <c r="V14"/>
-      <c r="W14"/>
-      <c r="X14"/>
-      <c r="Y14"/>
-      <c r="Z14"/>
-      <c r="AA14"/>
-      <c r="AB14"/>
-      <c r="AC14"/>
-    </row>
-    <row r="15" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="str">
-        <f>'Wikipedia table'!A18</f>
-        <v>Bristol</v>
-      </c>
-      <c r="B15" s="16">
-        <f>'Wikipedia table'!B18</f>
-        <v>3090</v>
-      </c>
-      <c r="C15" s="16">
-        <f>'Wikipedia table'!D18</f>
-        <v>1660</v>
-      </c>
-      <c r="D15" s="15">
-        <f>'Wikipedia table'!F18</f>
-        <v>7</v>
-      </c>
-      <c r="E15" s="16">
-        <f>SUM(B15:D15)</f>
-        <v>4757</v>
-      </c>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15"/>
-      <c r="N15"/>
-      <c r="O15"/>
-      <c r="P15"/>
-      <c r="Q15"/>
-      <c r="R15"/>
-      <c r="S15"/>
-      <c r="T15"/>
-      <c r="U15"/>
-      <c r="V15"/>
-      <c r="W15"/>
-      <c r="X15"/>
-      <c r="Y15"/>
-      <c r="Z15"/>
-      <c r="AA15"/>
-      <c r="AB15"/>
-      <c r="AC15"/>
-    </row>
-    <row r="16" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="str">
-        <f>'Wikipedia table'!A19</f>
-        <v>Brunswick</v>
-      </c>
-      <c r="B16" s="3">
-        <f>'Wikipedia table'!B19</f>
-        <v>2591</v>
-      </c>
-      <c r="C16" s="3">
-        <f>'Wikipedia table'!D19</f>
-        <v>3338</v>
-      </c>
-      <c r="D16">
-        <f>'Wikipedia table'!F19</f>
-        <v>5</v>
-      </c>
-      <c r="E16" s="3">
-        <f>SUM(B16:D16)</f>
-        <v>5934</v>
-      </c>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-      <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16"/>
-      <c r="N16"/>
-      <c r="O16"/>
-      <c r="P16"/>
-      <c r="Q16"/>
-      <c r="R16"/>
-      <c r="S16"/>
-      <c r="T16"/>
-      <c r="U16"/>
-      <c r="V16"/>
-      <c r="W16"/>
-      <c r="X16"/>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AA16"/>
-      <c r="AB16"/>
-      <c r="AC16"/>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A17" t="str">
-        <f>'Wikipedia table'!A20</f>
-        <v>Buchanan</v>
-      </c>
-      <c r="B17" s="3">
-        <f>'Wikipedia table'!B20</f>
-        <v>4434</v>
-      </c>
-      <c r="C17" s="3">
-        <f>'Wikipedia table'!D20</f>
-        <v>971</v>
-      </c>
-      <c r="D17">
-        <f>'Wikipedia table'!F20</f>
-        <v>8</v>
-      </c>
-      <c r="E17" s="3">
-        <f>SUM(B17:D17)</f>
-        <v>5413</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A18" t="str">
-        <f>'Wikipedia table'!A21</f>
-        <v>Buckingham</v>
-      </c>
-      <c r="B18" s="3">
-        <f>'Wikipedia table'!B21</f>
-        <v>3586</v>
-      </c>
-      <c r="C18" s="3">
-        <f>'Wikipedia table'!D21</f>
-        <v>2456</v>
-      </c>
-      <c r="D18">
-        <f>'Wikipedia table'!F21</f>
-        <v>13</v>
-      </c>
-      <c r="E18" s="3">
-        <f>SUM(B18:D18)</f>
-        <v>6055</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="str">
-        <f>'Wikipedia table'!A22</f>
-        <v>Buena Vista</v>
-      </c>
-      <c r="B19" s="3">
-        <f>'Wikipedia table'!B22</f>
-        <v>1392</v>
-      </c>
-      <c r="C19" s="3">
-        <f>'Wikipedia table'!D22</f>
-        <v>696</v>
-      </c>
-      <c r="D19">
-        <f>'Wikipedia table'!F22</f>
-        <v>9</v>
-      </c>
-      <c r="E19" s="3">
-        <f>SUM(B19:D19)</f>
-        <v>2097</v>
-      </c>
-      <c r="F19"/>
-      <c r="G19"/>
-      <c r="H19"/>
-      <c r="I19"/>
-      <c r="J19"/>
-      <c r="K19"/>
-      <c r="L19"/>
-      <c r="M19"/>
-      <c r="N19"/>
-      <c r="O19"/>
-      <c r="P19"/>
-      <c r="Q19"/>
-      <c r="R19"/>
-      <c r="S19"/>
-      <c r="T19"/>
-      <c r="U19"/>
-      <c r="V19"/>
-      <c r="W19"/>
-      <c r="X19"/>
-      <c r="Y19"/>
-      <c r="Z19"/>
-      <c r="AA19"/>
-      <c r="AB19"/>
-      <c r="AC19"/>
-    </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A20" t="str">
-        <f>'Wikipedia table'!A23</f>
-        <v>Campbell</v>
-      </c>
-      <c r="B20" s="3">
-        <f>'Wikipedia table'!B23</f>
-        <v>16878</v>
-      </c>
-      <c r="C20" s="3">
-        <f>'Wikipedia table'!D23</f>
-        <v>6130</v>
-      </c>
-      <c r="D20">
-        <f>'Wikipedia table'!F23</f>
-        <v>34</v>
-      </c>
-      <c r="E20" s="3">
-        <f>SUM(B20:D20)</f>
-        <v>23042</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A21" t="str">
-        <f>'Wikipedia table'!A24</f>
-        <v>Caroline</v>
-      </c>
-      <c r="B21" s="3">
-        <f>'Wikipedia table'!B24</f>
-        <v>6680</v>
-      </c>
-      <c r="C21" s="3">
-        <f>'Wikipedia table'!D24</f>
-        <v>6733</v>
-      </c>
-      <c r="D21">
-        <f>'Wikipedia table'!F24</f>
-        <v>23</v>
-      </c>
-      <c r="E21" s="3">
-        <f>SUM(B21:D21)</f>
-        <v>13436</v>
-      </c>
-    </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A22" t="str">
-        <f>'Wikipedia table'!A25</f>
-        <v>Carroll</v>
-      </c>
-      <c r="B22" s="3">
-        <f>'Wikipedia table'!B25</f>
-        <v>8889</v>
-      </c>
-      <c r="C22" s="3">
-        <f>'Wikipedia table'!D25</f>
-        <v>2433</v>
-      </c>
-      <c r="D22">
-        <f>'Wikipedia table'!F25</f>
-        <v>26</v>
-      </c>
-      <c r="E22" s="3">
-        <f>SUM(B22:D22)</f>
-        <v>11348</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A23" t="str">
-        <f>'Wikipedia table'!A26</f>
-        <v>Charles City</v>
-      </c>
-      <c r="B23" s="3">
-        <f>'Wikipedia table'!B26</f>
-        <v>1485</v>
-      </c>
-      <c r="C23" s="3">
-        <f>'Wikipedia table'!D26</f>
-        <v>2002</v>
-      </c>
-      <c r="D23">
-        <f>'Wikipedia table'!F26</f>
-        <v>5</v>
-      </c>
-      <c r="E23" s="3">
-        <f>SUM(B23:D23)</f>
-        <v>3492</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A24" t="str">
-        <f>'Wikipedia table'!A27</f>
-        <v>Charlotte</v>
-      </c>
-      <c r="B24" s="3">
-        <f>'Wikipedia table'!B27</f>
-        <v>3159</v>
-      </c>
-      <c r="C24" s="3">
-        <f>'Wikipedia table'!D27</f>
-        <v>1545</v>
-      </c>
-      <c r="D24">
-        <f>'Wikipedia table'!F27</f>
-        <v>6</v>
-      </c>
-      <c r="E24" s="3">
-        <f>SUM(B24:D24)</f>
-        <v>4710</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A25" t="str">
-        <f>'Wikipedia table'!A28</f>
-        <v>Charlottesville</v>
-      </c>
-      <c r="B25" s="3">
-        <f>'Wikipedia table'!B28</f>
-        <v>2056</v>
-      </c>
-      <c r="C25" s="3">
-        <f>'Wikipedia table'!D28</f>
-        <v>16799</v>
-      </c>
-      <c r="D25">
-        <f>'Wikipedia table'!F28</f>
-        <v>35</v>
-      </c>
-      <c r="E25" s="3">
-        <f>SUM(B25:D25)</f>
-        <v>18890</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="str">
-        <f>'Wikipedia table'!A29</f>
-        <v>Chesapeake</v>
-      </c>
-      <c r="B26" s="16">
-        <f>'Wikipedia table'!B29</f>
-        <v>42147</v>
-      </c>
-      <c r="C26" s="16">
-        <f>'Wikipedia table'!D29</f>
-        <v>53971</v>
-      </c>
-      <c r="D26" s="15">
-        <f>'Wikipedia table'!F29</f>
-        <v>164</v>
-      </c>
-      <c r="E26" s="16">
-        <f>SUM(B26:D26)</f>
-        <v>96282</v>
-      </c>
-      <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
-      <c r="I26"/>
-      <c r="J26"/>
-      <c r="K26"/>
-      <c r="L26"/>
-      <c r="M26"/>
-      <c r="N26"/>
-      <c r="O26"/>
-      <c r="P26"/>
-      <c r="Q26"/>
-      <c r="R26"/>
-      <c r="S26"/>
-      <c r="T26"/>
-      <c r="U26"/>
-      <c r="V26"/>
-      <c r="W26"/>
-      <c r="X26"/>
-      <c r="Y26"/>
-      <c r="Z26"/>
-      <c r="AA26"/>
-      <c r="AB26"/>
-      <c r="AC26"/>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="str">
-        <f>'Wikipedia table'!A30</f>
-        <v>Chesterfield</v>
-      </c>
-      <c r="B27" s="16">
-        <f>'Wikipedia table'!B30</f>
-        <v>70021</v>
-      </c>
-      <c r="C27" s="16">
-        <f>'Wikipedia table'!D30</f>
-        <v>100595</v>
-      </c>
-      <c r="D27" s="15">
-        <f>'Wikipedia table'!F30</f>
-        <v>294</v>
-      </c>
-      <c r="E27" s="16">
-        <f>SUM(B27:D27)</f>
-        <v>170910</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A28" t="str">
-        <f>'Wikipedia table'!A31</f>
-        <v>Clarke</v>
-      </c>
-      <c r="B28" s="3">
-        <f>'Wikipedia table'!B31</f>
-        <v>4222</v>
-      </c>
-      <c r="C28" s="3">
-        <f>'Wikipedia table'!D31</f>
-        <v>3389</v>
-      </c>
-      <c r="D28">
-        <f>'Wikipedia table'!F31</f>
-        <v>18</v>
-      </c>
-      <c r="E28" s="3">
-        <f>SUM(B28:D28)</f>
-        <v>7629</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A29" t="str">
-        <f>'Wikipedia table'!A32</f>
-        <v>Colonial Heights</v>
-      </c>
-      <c r="B29" s="3">
-        <f>'Wikipedia table'!B32</f>
-        <v>4092</v>
-      </c>
-      <c r="C29" s="3">
-        <f>'Wikipedia table'!D32</f>
-        <v>2474</v>
-      </c>
-      <c r="D29">
-        <f>'Wikipedia table'!F32</f>
-        <v>21</v>
-      </c>
-      <c r="E29" s="3">
-        <f>SUM(B29:D29)</f>
-        <v>6587</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A30" t="str">
-        <f>'Wikipedia table'!A33</f>
-        <v>Covington</v>
-      </c>
-      <c r="B30" s="3">
-        <f>'Wikipedia table'!B33</f>
-        <v>999</v>
-      </c>
-      <c r="C30" s="3">
-        <f>'Wikipedia table'!D33</f>
-        <v>678</v>
-      </c>
-      <c r="D30">
-        <f>'Wikipedia table'!F33</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="3">
-        <f>SUM(B30:D30)</f>
-        <v>1677</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A31" t="str">
-        <f>'Wikipedia table'!A34</f>
-        <v>Craig</v>
-      </c>
-      <c r="B31" s="3">
-        <f>'Wikipedia table'!B34</f>
-        <v>1806</v>
-      </c>
-      <c r="C31" s="3">
-        <f>'Wikipedia table'!D34</f>
-        <v>467</v>
-      </c>
-      <c r="D31">
-        <f>'Wikipedia table'!F34</f>
-        <v>6</v>
-      </c>
-      <c r="E31" s="3">
-        <f>SUM(B31:D31)</f>
-        <v>2279</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A32" t="str">
-        <f>'Wikipedia table'!A35</f>
-        <v>Culpeper</v>
-      </c>
-      <c r="B32" s="3">
-        <f>'Wikipedia table'!B35</f>
-        <v>12592</v>
-      </c>
-      <c r="C32" s="3">
-        <f>'Wikipedia table'!D35</f>
-        <v>9214</v>
-      </c>
-      <c r="D32">
-        <f>'Wikipedia table'!F35</f>
-        <v>33</v>
-      </c>
-      <c r="E32" s="3">
-        <f>SUM(B32:D32)</f>
-        <v>21839</v>
-      </c>
-    </row>
-    <row r="33" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" t="str">
-        <f>'Wikipedia table'!A36</f>
-        <v>Cumberland</v>
-      </c>
-      <c r="B33" s="3">
-        <f>'Wikipedia table'!B36</f>
-        <v>2609</v>
-      </c>
-      <c r="C33" s="3">
-        <f>'Wikipedia table'!D36</f>
-        <v>1803</v>
-      </c>
-      <c r="D33">
-        <f>'Wikipedia table'!F36</f>
-        <v>8</v>
-      </c>
-      <c r="E33" s="3">
-        <f>SUM(B33:D33)</f>
-        <v>4420</v>
-      </c>
-      <c r="F33"/>
-      <c r="G33"/>
-      <c r="H33"/>
-      <c r="I33"/>
-      <c r="J33"/>
-      <c r="K33"/>
-      <c r="L33"/>
-      <c r="M33"/>
-      <c r="N33"/>
-      <c r="O33"/>
-      <c r="P33"/>
-      <c r="Q33"/>
-      <c r="R33"/>
-      <c r="S33"/>
-      <c r="T33"/>
-      <c r="U33"/>
-      <c r="V33"/>
-      <c r="W33"/>
-      <c r="X33"/>
-      <c r="Y33"/>
-      <c r="Z33"/>
-      <c r="AA33"/>
-      <c r="AB33"/>
-      <c r="AC33"/>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A34" t="str">
-        <f>'Wikipedia table'!A37</f>
-        <v>Danville</v>
-      </c>
-      <c r="B34" s="3">
-        <f>'Wikipedia table'!B37</f>
-        <v>4592</v>
-      </c>
-      <c r="C34" s="3">
-        <f>'Wikipedia table'!D37</f>
-        <v>7678</v>
-      </c>
-      <c r="D34">
-        <f>'Wikipedia table'!F37</f>
-        <v>29</v>
-      </c>
-      <c r="E34" s="3">
-        <f>SUM(B34:D34)</f>
-        <v>12299</v>
-      </c>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A35" t="str">
-        <f>'Wikipedia table'!A38</f>
-        <v>Dickenson</v>
-      </c>
-      <c r="B35" s="3">
-        <f>'Wikipedia table'!B38</f>
-        <v>3427</v>
-      </c>
-      <c r="C35" s="3">
-        <f>'Wikipedia table'!D38</f>
-        <v>1028</v>
-      </c>
-      <c r="D35">
-        <f>'Wikipedia table'!F38</f>
-        <v>7</v>
-      </c>
-      <c r="E35" s="3">
-        <f>SUM(B35:D35)</f>
-        <v>4462</v>
-      </c>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A36" t="str">
-        <f>'Wikipedia table'!A39</f>
-        <v>Dinwiddie</v>
-      </c>
-      <c r="B36" s="3">
-        <f>'Wikipedia table'!B39</f>
-        <v>7028</v>
-      </c>
-      <c r="C36" s="3">
-        <f>'Wikipedia table'!D39</f>
-        <v>5031</v>
-      </c>
-      <c r="D36">
-        <f>'Wikipedia table'!F39</f>
-        <v>19</v>
-      </c>
-      <c r="E36" s="3">
-        <f>SUM(B36:D36)</f>
-        <v>12078</v>
-      </c>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A37" t="str">
-        <f>'Wikipedia table'!A40</f>
-        <v>Emporia</v>
-      </c>
-      <c r="B37" s="3">
-        <f>'Wikipedia table'!B40</f>
-        <v>544</v>
-      </c>
-      <c r="C37" s="3">
-        <f>'Wikipedia table'!D40</f>
-        <v>1119</v>
-      </c>
-      <c r="D37">
-        <f>'Wikipedia table'!F40</f>
-        <v>3</v>
-      </c>
-      <c r="E37" s="3">
-        <f>SUM(B37:D37)</f>
-        <v>1666</v>
-      </c>
-    </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A38" t="str">
-        <f>'Wikipedia table'!A41</f>
-        <v>Essex</v>
-      </c>
-      <c r="B38" s="3">
-        <f>'Wikipedia table'!B41</f>
-        <v>2572</v>
-      </c>
-      <c r="C38" s="3">
-        <f>'Wikipedia table'!D41</f>
-        <v>2289</v>
-      </c>
-      <c r="D38">
-        <f>'Wikipedia table'!F41</f>
-        <v>8</v>
-      </c>
-      <c r="E38" s="3">
-        <f>SUM(B38:D38)</f>
-        <v>4869</v>
-      </c>
-    </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A39" t="str">
-        <f>'Wikipedia table'!A42</f>
-        <v>Fairfax City</v>
-      </c>
-      <c r="B39" s="3">
-        <f>'Wikipedia table'!B42</f>
-        <v>2847</v>
-      </c>
-      <c r="C39" s="3">
-        <f>'Wikipedia table'!D42</f>
-        <v>7552</v>
-      </c>
-      <c r="D39">
-        <f>'Wikipedia table'!F42</f>
-        <v>36</v>
-      </c>
-      <c r="E39" s="3">
-        <f>SUM(B39:D39)</f>
-        <v>10435</v>
-      </c>
-    </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A40" s="15" t="str">
-        <f>'Wikipedia table'!A43</f>
-        <v>Fairfax County</v>
-      </c>
-      <c r="B40" s="16">
-        <f>'Wikipedia table'!B43</f>
-        <v>116053</v>
-      </c>
-      <c r="C40" s="16">
-        <f>'Wikipedia table'!D43</f>
-        <v>329977</v>
-      </c>
-      <c r="D40" s="15">
-        <f>'Wikipedia table'!F43</f>
-        <v>1222</v>
-      </c>
-      <c r="E40" s="16">
-        <f>SUM(B40:D40)</f>
-        <v>447252</v>
-      </c>
-    </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A41" t="str">
-        <f>'Wikipedia table'!A44</f>
-        <v>Falls Church</v>
-      </c>
-      <c r="B41" s="3">
-        <f>'Wikipedia table'!B44</f>
-        <v>1181</v>
-      </c>
-      <c r="C41" s="3">
-        <f>'Wikipedia table'!D44</f>
-        <v>6407</v>
-      </c>
-      <c r="D41">
-        <f>'Wikipedia table'!F44</f>
-        <v>12</v>
-      </c>
-      <c r="E41" s="3">
-        <f>SUM(B41:D41)</f>
-        <v>7600</v>
-      </c>
-    </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="str">
-        <f>'Wikipedia table'!A45</f>
-        <v>Fauquier</v>
-      </c>
-      <c r="B42" s="16">
-        <f>'Wikipedia table'!B45</f>
-        <v>19894</v>
-      </c>
-      <c r="C42" s="16">
-        <f>'Wikipedia table'!D45</f>
-        <v>14610</v>
-      </c>
-      <c r="D42" s="15">
-        <f>'Wikipedia table'!F45</f>
-        <v>62</v>
-      </c>
-      <c r="E42" s="16">
-        <f>SUM(B42:D42)</f>
-        <v>34566</v>
-      </c>
-    </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A43" t="str">
-        <f>'Wikipedia table'!A46</f>
-        <v>Floyd</v>
-      </c>
-      <c r="B43" s="3">
-        <f>'Wikipedia table'!B46</f>
-        <v>4806</v>
-      </c>
-      <c r="C43" s="3">
-        <f>'Wikipedia table'!D46</f>
-        <v>2603</v>
-      </c>
-      <c r="D43">
-        <f>'Wikipedia table'!F46</f>
-        <v>16</v>
-      </c>
-      <c r="E43" s="3">
-        <f>SUM(B43:D43)</f>
-        <v>7425</v>
-      </c>
-    </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A44" t="str">
-        <f>'Wikipedia table'!A47</f>
-        <v>Fluvanna</v>
-      </c>
-      <c r="B44" s="3">
-        <f>'Wikipedia table'!B47</f>
-        <v>6718</v>
-      </c>
-      <c r="C44" s="3">
-        <f>'Wikipedia table'!D47</f>
-        <v>6712</v>
-      </c>
-      <c r="D44">
-        <f>'Wikipedia table'!F47</f>
-        <v>19</v>
-      </c>
-      <c r="E44" s="3">
-        <f>SUM(B44:D44)</f>
-        <v>13449</v>
-      </c>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A45" t="str">
-        <f>'Wikipedia table'!A48</f>
-        <v>Franklin City</v>
-      </c>
-      <c r="B45" s="3">
-        <f>'Wikipedia table'!B48</f>
-        <v>1084</v>
-      </c>
-      <c r="C45" s="3">
-        <f>'Wikipedia table'!D48</f>
-        <v>1849</v>
-      </c>
-      <c r="D45">
-        <f>'Wikipedia table'!F48</f>
-        <v>2</v>
-      </c>
-      <c r="E45" s="3">
-        <f>SUM(B45:D45)</f>
-        <v>2935</v>
-      </c>
-    </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="str">
-        <f>'Wikipedia table'!A49</f>
-        <v>Franklin County</v>
-      </c>
-      <c r="B46" s="16">
-        <f>'Wikipedia table'!B49</f>
-        <v>16317</v>
-      </c>
-      <c r="C46" s="16">
-        <f>'Wikipedia table'!D49</f>
-        <v>6836</v>
-      </c>
-      <c r="D46" s="15">
-        <f>'Wikipedia table'!F49</f>
-        <v>36</v>
-      </c>
-      <c r="E46" s="16">
-        <f>SUM(B46:D46)</f>
-        <v>23189</v>
-      </c>
-    </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A47" t="str">
-        <f>'Wikipedia table'!A50</f>
-        <v>Frederick</v>
-      </c>
-      <c r="B47" s="3">
-        <f>'Wikipedia table'!B50</f>
-        <v>23130</v>
-      </c>
-      <c r="C47" s="3">
-        <f>'Wikipedia table'!D50</f>
-        <v>15809</v>
-      </c>
-      <c r="D47">
-        <f>'Wikipedia table'!F50</f>
-        <v>51</v>
-      </c>
-      <c r="E47" s="3">
-        <f>SUM(B47:D47)</f>
-        <v>38990</v>
-      </c>
-    </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A48" t="str">
-        <f>'Wikipedia table'!A51</f>
-        <v>Fredericksburg</v>
-      </c>
-      <c r="B48" s="3">
-        <f>'Wikipedia table'!B51</f>
-        <v>2943</v>
-      </c>
-      <c r="C48" s="3">
-        <f>'Wikipedia table'!D51</f>
-        <v>7561</v>
-      </c>
-      <c r="D48">
-        <f>'Wikipedia table'!F51</f>
-        <v>33</v>
-      </c>
-      <c r="E48" s="3">
-        <f>SUM(B48:D48)</f>
-        <v>10537</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="str">
-        <f>'Wikipedia table'!A52</f>
-        <v>Galax</v>
-      </c>
-      <c r="B49" s="3">
-        <f>'Wikipedia table'!B52</f>
-        <v>1284</v>
-      </c>
-      <c r="C49" s="3">
-        <f>'Wikipedia table'!D52</f>
-        <v>597</v>
-      </c>
-      <c r="D49">
-        <f>'Wikipedia table'!F52</f>
-        <v>1</v>
-      </c>
-      <c r="E49" s="3">
-        <f>SUM(B49:D49)</f>
-        <v>1882</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="str">
-        <f>'Wikipedia table'!A53</f>
-        <v>Giles</v>
-      </c>
-      <c r="B50" s="3">
-        <f>'Wikipedia table'!B53</f>
-        <v>4983</v>
-      </c>
-      <c r="C50" s="3">
-        <f>'Wikipedia table'!D53</f>
-        <v>1782</v>
-      </c>
-      <c r="D50">
-        <f>'Wikipedia table'!F53</f>
-        <v>16</v>
-      </c>
-      <c r="E50" s="3">
-        <f>SUM(B50:D50)</f>
-        <v>6781</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="str">
-        <f>'Wikipedia table'!A54</f>
-        <v>Gloucester</v>
-      </c>
-      <c r="B51" s="3">
-        <f>'Wikipedia table'!B54</f>
-        <v>11399</v>
-      </c>
-      <c r="C51" s="3">
-        <f>'Wikipedia table'!D54</f>
-        <v>5912</v>
-      </c>
-      <c r="D51">
-        <f>'Wikipedia table'!F54</f>
-        <v>30</v>
-      </c>
-      <c r="E51" s="3">
-        <f>SUM(B51:D51)</f>
-        <v>17341</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="str">
-        <f>'Wikipedia table'!A55</f>
-        <v>Goochland</v>
-      </c>
-      <c r="B52" s="3">
-        <f>'Wikipedia table'!B55</f>
-        <v>9726</v>
-      </c>
-      <c r="C52" s="3">
-        <f>'Wikipedia table'!D55</f>
-        <v>7339</v>
-      </c>
-      <c r="D52">
-        <f>'Wikipedia table'!F55</f>
-        <v>24</v>
-      </c>
-      <c r="E52" s="3">
-        <f>SUM(B52:D52)</f>
-        <v>17089</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="str">
-        <f>'Wikipedia table'!A56</f>
-        <v>Grayson</v>
-      </c>
-      <c r="B53" s="3">
-        <f>'Wikipedia table'!B56</f>
-        <v>4614</v>
-      </c>
-      <c r="C53" s="3">
-        <f>'Wikipedia table'!D56</f>
-        <v>1264</v>
-      </c>
-      <c r="D53">
-        <f>'Wikipedia table'!F56</f>
-        <v>11</v>
-      </c>
-      <c r="E53" s="3">
-        <f>SUM(B53:D53)</f>
-        <v>5889</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="str">
-        <f>'Wikipedia table'!A57</f>
-        <v>Greene</v>
-      </c>
-      <c r="B54" s="3">
-        <f>'Wikipedia table'!B57</f>
-        <v>5458</v>
-      </c>
-      <c r="C54" s="3">
-        <f>'Wikipedia table'!D57</f>
-        <v>4036</v>
-      </c>
-      <c r="D54">
-        <f>'Wikipedia table'!F57</f>
-        <v>16</v>
-      </c>
-      <c r="E54" s="3">
-        <f>SUM(B54:D54)</f>
-        <v>9510</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="str">
-        <f>'Wikipedia table'!A58</f>
-        <v>Greensville</v>
-      </c>
-      <c r="B55" s="3">
-        <f>'Wikipedia table'!B58</f>
-        <v>1427</v>
-      </c>
-      <c r="C55" s="3">
-        <f>'Wikipedia table'!D58</f>
-        <v>1902</v>
-      </c>
-      <c r="D55">
-        <f>'Wikipedia table'!F58</f>
-        <v>8</v>
-      </c>
-      <c r="E55" s="3">
-        <f>SUM(B55:D55)</f>
-        <v>3337</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="str">
-        <f>'Wikipedia table'!A59</f>
-        <v>Halifax</v>
-      </c>
-      <c r="B56" s="3">
-        <f>'Wikipedia table'!B59</f>
-        <v>8027</v>
-      </c>
-      <c r="C56" s="3">
-        <f>'Wikipedia table'!D59</f>
-        <v>5272</v>
-      </c>
-      <c r="D56">
-        <f>'Wikipedia table'!F59</f>
-        <v>22</v>
-      </c>
-      <c r="E56" s="3">
-        <f>SUM(B56:D56)</f>
-        <v>13321</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="str">
-        <f>'Wikipedia table'!A60</f>
-        <v>Hampton</v>
-      </c>
-      <c r="B57" s="3">
-        <f>'Wikipedia table'!B60</f>
-        <v>12103</v>
-      </c>
-      <c r="C57" s="3">
-        <f>'Wikipedia table'!D60</f>
-        <v>35129</v>
-      </c>
-      <c r="D57">
-        <f>'Wikipedia table'!F60</f>
-        <v>91</v>
-      </c>
-      <c r="E57" s="3">
-        <f>SUM(B57:D57)</f>
-        <v>47323</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="15" t="str">
-        <f>'Wikipedia table'!A61</f>
-        <v>Hanover</v>
-      </c>
-      <c r="B58" s="16">
-        <f>'Wikipedia table'!B61</f>
-        <v>36278</v>
-      </c>
-      <c r="C58" s="16">
-        <f>'Wikipedia table'!D61</f>
-        <v>23994</v>
-      </c>
-      <c r="D58" s="15">
-        <f>'Wikipedia table'!F61</f>
-        <v>95</v>
-      </c>
-      <c r="E58" s="16">
-        <f>SUM(B58:D58)</f>
-        <v>60367</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" t="str">
-        <f>'Wikipedia table'!A62</f>
-        <v>Harrisonburg</v>
-      </c>
-      <c r="B59" s="3">
-        <f>'Wikipedia table'!B62</f>
-        <v>3654</v>
-      </c>
-      <c r="C59" s="3">
-        <f>'Wikipedia table'!D62</f>
-        <v>9512</v>
-      </c>
-      <c r="D59">
-        <f>'Wikipedia table'!F62</f>
-        <v>23</v>
-      </c>
-      <c r="E59" s="3">
-        <f>SUM(B59:D59)</f>
-        <v>13189</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="15" t="str">
-        <f>'Wikipedia table'!A63</f>
-        <v>Henrico</v>
-      </c>
-      <c r="B60" s="16">
-        <f>'Wikipedia table'!B63</f>
-        <v>45627</v>
-      </c>
-      <c r="C60" s="16">
-        <f>'Wikipedia table'!D63</f>
-        <v>103559</v>
-      </c>
-      <c r="D60" s="15">
-        <f>'Wikipedia table'!F63</f>
-        <v>260</v>
-      </c>
-      <c r="E60" s="16">
-        <f>SUM(B60:D60)</f>
-        <v>149446</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" t="str">
-        <f>'Wikipedia table'!A64</f>
-        <v>Henry</v>
-      </c>
-      <c r="B61" s="3">
-        <f>'Wikipedia table'!B64</f>
-        <v>11150</v>
-      </c>
-      <c r="C61" s="3">
-        <f>'Wikipedia table'!D64</f>
-        <v>6320</v>
-      </c>
-      <c r="D61">
-        <f>'Wikipedia table'!F64</f>
-        <v>30</v>
-      </c>
-      <c r="E61" s="3">
-        <f>SUM(B61:D61)</f>
-        <v>17500</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="str">
-        <f>'Wikipedia table'!A65</f>
-        <v>Highland</v>
-      </c>
-      <c r="B62" s="3">
-        <f>'Wikipedia table'!B65</f>
-        <v>831</v>
-      </c>
-      <c r="C62" s="3">
-        <f>'Wikipedia table'!D65</f>
-        <v>362</v>
-      </c>
-      <c r="D62">
-        <f>'Wikipedia table'!F65</f>
-        <v>1</v>
-      </c>
-      <c r="E62" s="3">
-        <f>SUM(B62:D62)</f>
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" t="str">
-        <f>'Wikipedia table'!A66</f>
-        <v>Hopewell</v>
-      </c>
-      <c r="B63" s="3">
-        <f>'Wikipedia table'!B66</f>
-        <v>2610</v>
-      </c>
-      <c r="C63" s="3">
-        <f>'Wikipedia table'!D66</f>
-        <v>4052</v>
-      </c>
-      <c r="D63">
-        <f>'Wikipedia table'!F66</f>
-        <v>13</v>
-      </c>
-      <c r="E63" s="3">
-        <f>SUM(B63:D63)</f>
-        <v>6675</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" t="str">
-        <f>'Wikipedia table'!A67</f>
-        <v>Isle of Wight</v>
-      </c>
-      <c r="B64" s="3">
-        <f>'Wikipedia table'!B67</f>
-        <v>10931</v>
-      </c>
-      <c r="C64" s="3">
-        <f>'Wikipedia table'!D67</f>
-        <v>8227</v>
-      </c>
-      <c r="D64">
-        <f>'Wikipedia table'!F67</f>
-        <v>37</v>
-      </c>
-      <c r="E64" s="3">
-        <f>SUM(B64:D64)</f>
-        <v>19195</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" t="str">
-        <f>'Wikipedia table'!A68</f>
-        <v>James City</v>
-      </c>
-      <c r="B65" s="3">
-        <f>'Wikipedia table'!B68</f>
-        <v>19029</v>
-      </c>
-      <c r="C65" s="3">
-        <f>'Wikipedia table'!D68</f>
-        <v>23603</v>
-      </c>
-      <c r="D65">
-        <f>'Wikipedia table'!F68</f>
-        <v>63</v>
-      </c>
-      <c r="E65" s="3">
-        <f>SUM(B65:D65)</f>
-        <v>42695</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" t="str">
-        <f>'Wikipedia table'!A69</f>
-        <v>King and Queen</v>
-      </c>
-      <c r="B66" s="3">
-        <f>'Wikipedia table'!B69</f>
-        <v>1985</v>
-      </c>
-      <c r="C66" s="3">
-        <f>'Wikipedia table'!D69</f>
-        <v>1292</v>
-      </c>
-      <c r="D66">
-        <f>'Wikipedia table'!F69</f>
-        <v>4</v>
-      </c>
-      <c r="E66" s="3">
-        <f>SUM(B66:D66)</f>
-        <v>3281</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" t="str">
-        <f>'Wikipedia table'!A70</f>
-        <v>King George</v>
-      </c>
-      <c r="B67" s="3">
-        <f>'Wikipedia table'!B70</f>
-        <v>6909</v>
-      </c>
-      <c r="C67" s="3">
-        <f>'Wikipedia table'!D70</f>
-        <v>4716</v>
-      </c>
-      <c r="D67">
-        <f>'Wikipedia table'!F70</f>
-        <v>20</v>
-      </c>
-      <c r="E67" s="3">
-        <f>SUM(B67:D67)</f>
-        <v>11645</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" t="str">
-        <f>'Wikipedia table'!A71</f>
-        <v>King William</v>
-      </c>
-      <c r="B68" s="3">
-        <f>'Wikipedia table'!B71</f>
-        <v>6033</v>
-      </c>
-      <c r="C68" s="3">
-        <f>'Wikipedia table'!D71</f>
-        <v>3020</v>
-      </c>
-      <c r="D68">
-        <f>'Wikipedia table'!F71</f>
-        <v>11</v>
-      </c>
-      <c r="E68" s="3">
-        <f>SUM(B68:D68)</f>
-        <v>9064</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" t="str">
-        <f>'Wikipedia table'!A72</f>
-        <v>Lancaster</v>
-      </c>
-      <c r="B69" s="3">
-        <f>'Wikipedia table'!B72</f>
-        <v>3283</v>
-      </c>
-      <c r="C69" s="3">
-        <f>'Wikipedia table'!D72</f>
-        <v>2734</v>
-      </c>
-      <c r="D69">
-        <f>'Wikipedia table'!F72</f>
-        <v>13</v>
-      </c>
-      <c r="E69" s="3">
-        <f>SUM(B69:D69)</f>
-        <v>6030</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="15" t="str">
-        <f>'Wikipedia table'!A73</f>
-        <v>Lee</v>
-      </c>
-      <c r="B70" s="16">
-        <f>'Wikipedia table'!B73</f>
-        <v>5439</v>
-      </c>
-      <c r="C70" s="16">
-        <f>'Wikipedia table'!D73</f>
-        <v>1019</v>
-      </c>
-      <c r="D70" s="15">
-        <f>'Wikipedia table'!F73</f>
-        <v>7</v>
-      </c>
-      <c r="E70" s="16">
-        <f>SUM(B70:D70)</f>
-        <v>6465</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="str">
-        <f>'Wikipedia table'!A74</f>
-        <v>Lexington</v>
-      </c>
-      <c r="B71" s="3">
-        <f>'Wikipedia table'!B74</f>
-        <v>686</v>
-      </c>
-      <c r="C71" s="3">
-        <f>'Wikipedia table'!D74</f>
-        <v>1475</v>
-      </c>
-      <c r="D71">
-        <f>'Wikipedia table'!F74</f>
-        <v>6</v>
-      </c>
-      <c r="E71" s="3">
-        <f>SUM(B71:D71)</f>
-        <v>2167</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="15" t="str">
-        <f>'Wikipedia table'!A75</f>
-        <v>Loudoun</v>
-      </c>
-      <c r="B72" s="16">
-        <f>'Wikipedia table'!B75</f>
-        <v>59278</v>
-      </c>
-      <c r="C72" s="16">
-        <f>'Wikipedia table'!D75</f>
-        <v>108594</v>
-      </c>
-      <c r="D72" s="15">
-        <f>'Wikipedia table'!F75</f>
-        <v>444</v>
-      </c>
-      <c r="E72" s="16">
-        <f>SUM(B72:D72)</f>
-        <v>168316</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="str">
-        <f>'Wikipedia table'!A76</f>
-        <v>Louisa</v>
-      </c>
-      <c r="B73" s="3">
-        <f>'Wikipedia table'!B76</f>
-        <v>11279</v>
-      </c>
-      <c r="C73" s="3">
-        <f>'Wikipedia table'!D76</f>
-        <v>7628</v>
-      </c>
-      <c r="D73">
-        <f>'Wikipedia table'!F76</f>
-        <v>44</v>
-      </c>
-      <c r="E73" s="3">
-        <f>SUM(B73:D73)</f>
-        <v>18951</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" t="str">
-        <f>'Wikipedia table'!A77</f>
-        <v>Lunenburg</v>
-      </c>
-      <c r="B74" s="3">
-        <f>'Wikipedia table'!B77</f>
-        <v>2682</v>
-      </c>
-      <c r="C74" s="3">
-        <f>'Wikipedia table'!D77</f>
-        <v>1806</v>
-      </c>
-      <c r="D74">
-        <f>'Wikipedia table'!F77</f>
-        <v>11</v>
-      </c>
-      <c r="E74" s="3">
-        <f>SUM(B74:D74)</f>
-        <v>4499</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" t="str">
-        <f>'Wikipedia table'!A78</f>
-        <v>Lynchburg</v>
-      </c>
-      <c r="B75" s="3">
-        <f>'Wikipedia table'!B78</f>
-        <v>13508</v>
-      </c>
-      <c r="C75" s="3">
-        <f>'Wikipedia table'!D78</f>
-        <v>13231</v>
-      </c>
-      <c r="D75">
-        <f>'Wikipedia table'!F78</f>
-        <v>56</v>
-      </c>
-      <c r="E75" s="3">
-        <f>SUM(B75:D75)</f>
-        <v>26795</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" t="str">
-        <f>'Wikipedia table'!A79</f>
-        <v>Madison</v>
-      </c>
-      <c r="B76" s="3">
-        <f>'Wikipedia table'!B79</f>
-        <v>4259</v>
-      </c>
-      <c r="C76" s="3">
-        <f>'Wikipedia table'!D79</f>
-        <v>2386</v>
-      </c>
-      <c r="D76">
-        <f>'Wikipedia table'!F79</f>
-        <v>9</v>
-      </c>
-      <c r="E76" s="3">
-        <f>SUM(B76:D76)</f>
-        <v>6654</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" t="str">
-        <f>'Wikipedia table'!A80</f>
-        <v>Manassas</v>
-      </c>
-      <c r="B77" s="3">
-        <f>'Wikipedia table'!B80</f>
-        <v>4036</v>
-      </c>
-      <c r="C77" s="3">
-        <f>'Wikipedia table'!D80</f>
-        <v>7671</v>
-      </c>
-      <c r="D77">
-        <f>'Wikipedia table'!F80</f>
-        <v>18</v>
-      </c>
-      <c r="E77" s="3">
-        <f>SUM(B77:D77)</f>
-        <v>11725</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" t="str">
-        <f>'Wikipedia table'!A81</f>
-        <v>Manassas Park</v>
-      </c>
-      <c r="B78" s="3">
-        <f>'Wikipedia table'!B81</f>
-        <v>1151</v>
-      </c>
-      <c r="C78" s="3">
-        <f>'Wikipedia table'!D81</f>
-        <v>2852</v>
-      </c>
-      <c r="D78">
-        <f>'Wikipedia table'!F81</f>
-        <v>5</v>
-      </c>
-      <c r="E78" s="3">
-        <f>SUM(B78:D78)</f>
-        <v>4008</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" t="str">
-        <f>'Wikipedia table'!A82</f>
-        <v>Martinsville</v>
-      </c>
-      <c r="B79" s="3">
-        <f>'Wikipedia table'!B82</f>
-        <v>1451</v>
-      </c>
-      <c r="C79" s="3">
-        <f>'Wikipedia table'!D82</f>
-        <v>2534</v>
-      </c>
-      <c r="D79">
-        <f>'Wikipedia table'!F82</f>
-        <v>7</v>
-      </c>
-      <c r="E79" s="3">
-        <f>SUM(B79:D79)</f>
-        <v>3992</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" t="str">
-        <f>'Wikipedia table'!A83</f>
-        <v>Mathews</v>
-      </c>
-      <c r="B80" s="3">
-        <f>'Wikipedia table'!B83</f>
-        <v>3242</v>
-      </c>
-      <c r="C80" s="3">
-        <f>'Wikipedia table'!D83</f>
-        <v>1555</v>
-      </c>
-      <c r="D80">
-        <f>'Wikipedia table'!F83</f>
-        <v>5</v>
-      </c>
-      <c r="E80" s="3">
-        <f>SUM(B80:D80)</f>
-        <v>4802</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" t="str">
-        <f>'Wikipedia table'!A84</f>
-        <v>Mecklenburg</v>
-      </c>
-      <c r="B81" s="3">
-        <f>'Wikipedia table'!B84</f>
-        <v>7151</v>
-      </c>
-      <c r="C81" s="3">
-        <f>'Wikipedia table'!D84</f>
-        <v>4657</v>
-      </c>
-      <c r="D81">
-        <f>'Wikipedia table'!F84</f>
-        <v>11</v>
-      </c>
-      <c r="E81" s="3">
-        <f>SUM(B81:D81)</f>
-        <v>11819</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" t="str">
-        <f>'Wikipedia table'!A85</f>
-        <v>Middlesex</v>
-      </c>
-      <c r="B82" s="3">
-        <f>'Wikipedia table'!B85</f>
-        <v>3473</v>
-      </c>
-      <c r="C82" s="3">
-        <f>'Wikipedia table'!D85</f>
-        <v>2174</v>
-      </c>
-      <c r="D82">
-        <f>'Wikipedia table'!F85</f>
-        <v>6</v>
-      </c>
-      <c r="E82" s="3">
-        <f>SUM(B82:D82)</f>
-        <v>5653</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" t="str">
-        <f>'Wikipedia table'!A86</f>
-        <v>Montgomery</v>
-      </c>
-      <c r="B83" s="3">
-        <f>'Wikipedia table'!B86</f>
-        <v>15228</v>
-      </c>
-      <c r="C83" s="3">
-        <f>'Wikipedia table'!D86</f>
-        <v>21428</v>
-      </c>
-      <c r="D83">
-        <f>'Wikipedia table'!F86</f>
-        <v>76</v>
-      </c>
-      <c r="E83" s="3">
-        <f>SUM(B83:D83)</f>
-        <v>36732</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" t="str">
-        <f>'Wikipedia table'!A87</f>
-        <v>Nelson</v>
-      </c>
-      <c r="B84" s="3">
-        <f>'Wikipedia table'!B87</f>
-        <v>3828</v>
-      </c>
-      <c r="C84" s="3">
-        <f>'Wikipedia table'!D87</f>
-        <v>3880</v>
-      </c>
-      <c r="D84">
-        <f>'Wikipedia table'!F87</f>
-        <v>17</v>
-      </c>
-      <c r="E84" s="3">
-        <f>SUM(B84:D84)</f>
-        <v>7725</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" t="str">
-        <f>'Wikipedia table'!A88</f>
-        <v>New Kent</v>
-      </c>
-      <c r="B85" s="3">
-        <f>'Wikipedia table'!B88</f>
-        <v>8804</v>
-      </c>
-      <c r="C85" s="3">
-        <f>'Wikipedia table'!D88</f>
-        <v>5087</v>
-      </c>
-      <c r="D85">
-        <f>'Wikipedia table'!F88</f>
-        <v>22</v>
-      </c>
-      <c r="E85" s="3">
-        <f>SUM(B85:D85)</f>
-        <v>13913</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="15" t="str">
-        <f>'Wikipedia table'!A89</f>
-        <v>Newport News</v>
-      </c>
-      <c r="B86" s="16">
-        <f>'Wikipedia table'!B89</f>
-        <v>17461</v>
-      </c>
-      <c r="C86" s="16">
-        <f>'Wikipedia table'!D89</f>
-        <v>38936</v>
-      </c>
-      <c r="D86" s="15">
-        <f>'Wikipedia table'!F89</f>
-        <v>92</v>
-      </c>
-      <c r="E86" s="16">
-        <f>SUM(B86:D86)</f>
-        <v>56489</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="15" t="str">
-        <f>'Wikipedia table'!A90</f>
-        <v>Norfolk</v>
-      </c>
-      <c r="B87" s="16">
-        <f>'Wikipedia table'!B90</f>
-        <v>15509</v>
-      </c>
-      <c r="C87" s="16">
-        <f>'Wikipedia table'!D90</f>
-        <v>48599</v>
-      </c>
-      <c r="D87" s="15">
-        <f>'Wikipedia table'!F90</f>
-        <v>111</v>
-      </c>
-      <c r="E87" s="16">
-        <f>SUM(B87:D87)</f>
-        <v>64219</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="15" t="str">
-        <f>'Wikipedia table'!A91</f>
-        <v>Northampton</v>
-      </c>
-      <c r="B88" s="16">
-        <f>'Wikipedia table'!B91</f>
-        <v>2469</v>
-      </c>
-      <c r="C88" s="16">
-        <f>'Wikipedia table'!D91</f>
-        <v>3060</v>
-      </c>
-      <c r="D88" s="15">
-        <f>'Wikipedia table'!F91</f>
-        <v>8</v>
-      </c>
-      <c r="E88" s="16">
-        <f>SUM(B88:D88)</f>
-        <v>5537</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" t="str">
-        <f>'Wikipedia table'!A92</f>
-        <v>Northumberland</v>
-      </c>
-      <c r="B89" s="3">
-        <f>'Wikipedia table'!B92</f>
-        <v>4132</v>
-      </c>
-      <c r="C89" s="3">
-        <f>'Wikipedia table'!D92</f>
-        <v>2685</v>
-      </c>
-      <c r="D89">
-        <f>'Wikipedia table'!F92</f>
-        <v>16</v>
-      </c>
-      <c r="E89" s="3">
-        <f>SUM(B89:D89)</f>
-        <v>6833</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" t="str">
-        <f>'Wikipedia table'!A93</f>
-        <v>Norton</v>
-      </c>
-      <c r="B90" s="3">
-        <f>'Wikipedia table'!B93</f>
-        <v>721</v>
-      </c>
-      <c r="C90" s="3">
-        <f>'Wikipedia table'!D93</f>
-        <v>332</v>
-      </c>
-      <c r="D90">
-        <f>'Wikipedia table'!F93</f>
-        <v>2</v>
-      </c>
-      <c r="E90" s="3">
-        <f>SUM(B90:D90)</f>
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" t="str">
-        <f>'Wikipedia table'!A94</f>
-        <v>Nottoway</v>
-      </c>
-      <c r="B91" s="3">
-        <f>'Wikipedia table'!B94</f>
-        <v>3122</v>
-      </c>
-      <c r="C91" s="3">
-        <f>'Wikipedia table'!D94</f>
-        <v>2258</v>
-      </c>
-      <c r="D91">
-        <f>'Wikipedia table'!F94</f>
-        <v>11</v>
-      </c>
-      <c r="E91" s="3">
-        <f>SUM(B91:D91)</f>
-        <v>5391</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" t="str">
-        <f>'Wikipedia table'!A95</f>
-        <v>Orange</v>
-      </c>
-      <c r="B92" s="3">
-        <f>'Wikipedia table'!B95</f>
-        <v>9938</v>
-      </c>
-      <c r="C92" s="3">
-        <f>'Wikipedia table'!D95</f>
-        <v>7361</v>
-      </c>
-      <c r="D92">
-        <f>'Wikipedia table'!F95</f>
-        <v>33</v>
-      </c>
-      <c r="E92" s="3">
-        <f>SUM(B92:D92)</f>
-        <v>17332</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" t="str">
-        <f>'Wikipedia table'!A96</f>
-        <v>Page</v>
-      </c>
-      <c r="B93" s="3">
-        <f>'Wikipedia table'!B96</f>
-        <v>6940</v>
-      </c>
-      <c r="C93" s="3">
-        <f>'Wikipedia table'!D96</f>
-        <v>2365</v>
-      </c>
-      <c r="D93">
-        <f>'Wikipedia table'!F96</f>
-        <v>24</v>
-      </c>
-      <c r="E93" s="3">
-        <f>SUM(B93:D93)</f>
-        <v>9329</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" t="str">
-        <f>'Wikipedia table'!A97</f>
-        <v>Patrick</v>
-      </c>
-      <c r="B94" s="3">
-        <f>'Wikipedia table'!B97</f>
-        <v>5119</v>
-      </c>
-      <c r="C94" s="3">
-        <f>'Wikipedia table'!D97</f>
-        <v>1488</v>
-      </c>
-      <c r="D94">
-        <f>'Wikipedia table'!F97</f>
-        <v>5</v>
-      </c>
-      <c r="E94" s="3">
-        <f>SUM(B94:D94)</f>
-        <v>6612</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" t="str">
-        <f>'Wikipedia table'!A98</f>
-        <v>Petersburg</v>
-      </c>
-      <c r="B95" s="3">
-        <f>'Wikipedia table'!B98</f>
-        <v>1124</v>
-      </c>
-      <c r="C95" s="3">
-        <f>'Wikipedia table'!D98</f>
-        <v>8811</v>
-      </c>
-      <c r="D95">
-        <f>'Wikipedia table'!F98</f>
-        <v>25</v>
-      </c>
-      <c r="E95" s="3">
-        <f>SUM(B95:D95)</f>
-        <v>9960</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" t="str">
-        <f>'Wikipedia table'!A99</f>
-        <v>Pittsylvania</v>
-      </c>
-      <c r="B96" s="3">
-        <f>'Wikipedia table'!B99</f>
-        <v>17439</v>
-      </c>
-      <c r="C96" s="3">
-        <f>'Wikipedia table'!D99</f>
-        <v>7272</v>
-      </c>
-      <c r="D96">
-        <f>'Wikipedia table'!F99</f>
-        <v>38</v>
-      </c>
       <c r="E96" s="3">
         <f>SUM(B96:D96)</f>
-        <v>24749</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6360</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="str">
         <f>'Wikipedia table'!A100</f>
         <v>Poquoson</v>
@@ -3978,1111 +3538,1111 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="str">
-        <f>'Wikipedia table'!A101</f>
-        <v>Portsmouth</v>
+        <f>'Wikipedia table'!A21</f>
+        <v>Buckingham</v>
       </c>
       <c r="B98" s="3">
-        <f>'Wikipedia table'!B101</f>
-        <v>8351</v>
+        <f>'Wikipedia table'!B21</f>
+        <v>3586</v>
       </c>
       <c r="C98" s="3">
-        <f>'Wikipedia table'!D101</f>
-        <v>23040</v>
+        <f>'Wikipedia table'!D21</f>
+        <v>2456</v>
       </c>
       <c r="D98">
-        <f>'Wikipedia table'!F101</f>
-        <v>62</v>
+        <f>'Wikipedia table'!F21</f>
+        <v>13</v>
       </c>
       <c r="E98" s="3">
         <f>SUM(B98:D98)</f>
-        <v>31453</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6055</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="str">
-        <f>'Wikipedia table'!A102</f>
-        <v>Powhatan</v>
+        <f>'Wikipedia table'!A72</f>
+        <v>Lancaster</v>
       </c>
       <c r="B99" s="3">
-        <f>'Wikipedia table'!B102</f>
-        <v>11862</v>
+        <f>'Wikipedia table'!B72</f>
+        <v>3283</v>
       </c>
       <c r="C99" s="3">
-        <f>'Wikipedia table'!D102</f>
-        <v>5168</v>
+        <f>'Wikipedia table'!D72</f>
+        <v>2734</v>
       </c>
       <c r="D99">
-        <f>'Wikipedia table'!F102</f>
-        <v>21</v>
+        <f>'Wikipedia table'!F72</f>
+        <v>13</v>
       </c>
       <c r="E99" s="3">
         <f>SUM(B99:D99)</f>
-        <v>17051</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6030</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="str">
-        <f>'Wikipedia table'!A103</f>
-        <v>Prince Edward</v>
+        <f>'Wikipedia table'!A19</f>
+        <v>Brunswick</v>
       </c>
       <c r="B100" s="3">
-        <f>'Wikipedia table'!B103</f>
-        <v>3668</v>
+        <f>'Wikipedia table'!B19</f>
+        <v>2591</v>
       </c>
       <c r="C100" s="3">
-        <f>'Wikipedia table'!D103</f>
-        <v>3767</v>
+        <f>'Wikipedia table'!D19</f>
+        <v>3338</v>
       </c>
       <c r="D100">
-        <f>'Wikipedia table'!F103</f>
-        <v>20</v>
+        <f>'Wikipedia table'!F19</f>
+        <v>5</v>
       </c>
       <c r="E100" s="3">
         <f>SUM(B100:D100)</f>
-        <v>7455</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5934</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="str">
-        <f>'Wikipedia table'!A104</f>
-        <v>Prince George</v>
+        <f>'Wikipedia table'!A56</f>
+        <v>Grayson</v>
       </c>
       <c r="B101" s="3">
-        <f>'Wikipedia table'!B104</f>
-        <v>7986</v>
+        <f>'Wikipedia table'!B56</f>
+        <v>4614</v>
       </c>
       <c r="C101" s="3">
-        <f>'Wikipedia table'!D104</f>
-        <v>5707</v>
+        <f>'Wikipedia table'!D56</f>
+        <v>1264</v>
       </c>
       <c r="D101">
-        <f>'Wikipedia table'!F104</f>
-        <v>13</v>
+        <f>'Wikipedia table'!F56</f>
+        <v>11</v>
       </c>
       <c r="E101" s="3">
         <f>SUM(B101:D101)</f>
-        <v>13706</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="15" t="str">
-        <f>'Wikipedia table'!A105</f>
-        <v>Prince William</v>
-      </c>
-      <c r="B102" s="16">
-        <f>'Wikipedia table'!B105</f>
-        <v>54309</v>
-      </c>
-      <c r="C102" s="16">
-        <f>'Wikipedia table'!D105</f>
-        <v>111198</v>
-      </c>
-      <c r="D102" s="15">
-        <f>'Wikipedia table'!F105</f>
-        <v>381</v>
-      </c>
-      <c r="E102" s="16">
+        <v>5889</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" t="str">
+        <f>'Wikipedia table'!A8</f>
+        <v>Alleghany</v>
+      </c>
+      <c r="B102" s="3">
+        <f>'Wikipedia table'!B8</f>
+        <v>4011</v>
+      </c>
+      <c r="C102" s="3">
+        <f>'Wikipedia table'!D8</f>
+        <v>1779</v>
+      </c>
+      <c r="D102">
+        <f>'Wikipedia table'!F8</f>
+        <v>11</v>
+      </c>
+      <c r="E102" s="3">
         <f>SUM(B102:D102)</f>
-        <v>165888</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5801</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="str">
-        <f>'Wikipedia table'!A106</f>
-        <v>Pulaski</v>
+        <f>'Wikipedia table'!A85</f>
+        <v>Middlesex</v>
       </c>
       <c r="B103" s="3">
-        <f>'Wikipedia table'!B106</f>
-        <v>8607</v>
+        <f>'Wikipedia table'!B85</f>
+        <v>3473</v>
       </c>
       <c r="C103" s="3">
-        <f>'Wikipedia table'!D106</f>
-        <v>3927</v>
+        <f>'Wikipedia table'!D85</f>
+        <v>2174</v>
       </c>
       <c r="D103">
-        <f>'Wikipedia table'!F106</f>
-        <v>22</v>
+        <f>'Wikipedia table'!F85</f>
+        <v>6</v>
       </c>
       <c r="E103" s="3">
         <f>SUM(B103:D103)</f>
-        <v>12556</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5653</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="str">
+        <f>'Wikipedia table'!A91</f>
+        <v>Northampton</v>
+      </c>
+      <c r="B104" s="3">
+        <f>'Wikipedia table'!B91</f>
+        <v>2469</v>
+      </c>
+      <c r="C104" s="3">
+        <f>'Wikipedia table'!D91</f>
+        <v>3060</v>
+      </c>
+      <c r="D104">
+        <f>'Wikipedia table'!F91</f>
+        <v>8</v>
+      </c>
+      <c r="E104" s="3">
+        <f>SUM(B104:D104)</f>
+        <v>5537</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" t="str">
+        <f>'Wikipedia table'!A20</f>
+        <v>Buchanan</v>
+      </c>
+      <c r="B105" s="3">
+        <f>'Wikipedia table'!B20</f>
+        <v>4434</v>
+      </c>
+      <c r="C105" s="3">
+        <f>'Wikipedia table'!D20</f>
+        <v>971</v>
+      </c>
+      <c r="D105">
+        <f>'Wikipedia table'!F20</f>
+        <v>8</v>
+      </c>
+      <c r="E105" s="3">
+        <f>SUM(B105:D105)</f>
+        <v>5413</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" t="str">
+        <f>'Wikipedia table'!A94</f>
+        <v>Nottoway</v>
+      </c>
+      <c r="B106" s="3">
+        <f>'Wikipedia table'!B94</f>
+        <v>3122</v>
+      </c>
+      <c r="C106" s="3">
+        <f>'Wikipedia table'!D94</f>
+        <v>2258</v>
+      </c>
+      <c r="D106">
+        <f>'Wikipedia table'!F94</f>
+        <v>11</v>
+      </c>
+      <c r="E106" s="3">
+        <f>SUM(B106:D106)</f>
+        <v>5391</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" t="str">
+        <f>'Wikipedia table'!A41</f>
+        <v>Essex</v>
+      </c>
+      <c r="B107" s="3">
+        <f>'Wikipedia table'!B41</f>
+        <v>2572</v>
+      </c>
+      <c r="C107" s="3">
+        <f>'Wikipedia table'!D41</f>
+        <v>2289</v>
+      </c>
+      <c r="D107">
+        <f>'Wikipedia table'!F41</f>
+        <v>8</v>
+      </c>
+      <c r="E107" s="3">
+        <f>SUM(B107:D107)</f>
+        <v>4869</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" t="str">
+        <f>'Wikipedia table'!A83</f>
+        <v>Mathews</v>
+      </c>
+      <c r="B108" s="3">
+        <f>'Wikipedia table'!B83</f>
+        <v>3242</v>
+      </c>
+      <c r="C108" s="3">
+        <f>'Wikipedia table'!D83</f>
+        <v>1555</v>
+      </c>
+      <c r="D108">
+        <f>'Wikipedia table'!F83</f>
+        <v>5</v>
+      </c>
+      <c r="E108" s="3">
+        <f>SUM(B108:D108)</f>
+        <v>4802</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" t="str">
+        <f>'Wikipedia table'!A18</f>
+        <v>Bristol</v>
+      </c>
+      <c r="B109" s="3">
+        <f>'Wikipedia table'!B18</f>
+        <v>3090</v>
+      </c>
+      <c r="C109" s="3">
+        <f>'Wikipedia table'!D18</f>
+        <v>1660</v>
+      </c>
+      <c r="D109">
+        <f>'Wikipedia table'!F18</f>
+        <v>7</v>
+      </c>
+      <c r="E109" s="3">
+        <f>SUM(B109:D109)</f>
+        <v>4757</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" t="str">
+        <f>'Wikipedia table'!A27</f>
+        <v>Charlotte</v>
+      </c>
+      <c r="B110" s="3">
+        <f>'Wikipedia table'!B27</f>
+        <v>3159</v>
+      </c>
+      <c r="C110" s="3">
+        <f>'Wikipedia table'!D27</f>
+        <v>1545</v>
+      </c>
+      <c r="D110">
+        <f>'Wikipedia table'!F27</f>
+        <v>6</v>
+      </c>
+      <c r="E110" s="3">
+        <f>SUM(B110:D110)</f>
+        <v>4710</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" t="str">
         <f>'Wikipedia table'!A107</f>
         <v>Radford</v>
       </c>
-      <c r="B104" s="3">
+      <c r="B111" s="3">
         <f>'Wikipedia table'!B107</f>
         <v>2050</v>
       </c>
-      <c r="C104" s="3">
+      <c r="C111" s="3">
         <f>'Wikipedia table'!D107</f>
         <v>2632</v>
       </c>
-      <c r="D104">
+      <c r="D111">
         <f>'Wikipedia table'!F107</f>
         <v>11</v>
       </c>
-      <c r="E104" s="3">
-        <f>SUM(B104:D104)</f>
+      <c r="E111" s="3">
+        <f>SUM(B111:D111)</f>
         <v>4693</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" t="str">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" t="str">
+        <f>'Wikipedia table'!A77</f>
+        <v>Lunenburg</v>
+      </c>
+      <c r="B112" s="3">
+        <f>'Wikipedia table'!B77</f>
+        <v>2682</v>
+      </c>
+      <c r="C112" s="3">
+        <f>'Wikipedia table'!D77</f>
+        <v>1806</v>
+      </c>
+      <c r="D112">
+        <f>'Wikipedia table'!F77</f>
+        <v>11</v>
+      </c>
+      <c r="E112" s="3">
+        <f>SUM(B112:D112)</f>
+        <v>4499</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" t="str">
+        <f>'Wikipedia table'!A38</f>
+        <v>Dickenson</v>
+      </c>
+      <c r="B113" s="3">
+        <f>'Wikipedia table'!B38</f>
+        <v>3427</v>
+      </c>
+      <c r="C113" s="3">
+        <f>'Wikipedia table'!D38</f>
+        <v>1028</v>
+      </c>
+      <c r="D113">
+        <f>'Wikipedia table'!F38</f>
+        <v>7</v>
+      </c>
+      <c r="E113" s="3">
+        <f>SUM(B113:D113)</f>
+        <v>4462</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" t="str">
+        <f>'Wikipedia table'!A36</f>
+        <v>Cumberland</v>
+      </c>
+      <c r="B114" s="3">
+        <f>'Wikipedia table'!B36</f>
+        <v>2609</v>
+      </c>
+      <c r="C114" s="3">
+        <f>'Wikipedia table'!D36</f>
+        <v>1803</v>
+      </c>
+      <c r="D114">
+        <f>'Wikipedia table'!F36</f>
+        <v>8</v>
+      </c>
+      <c r="E114" s="3">
+        <f>SUM(B114:D114)</f>
+        <v>4420</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" t="str">
         <f>'Wikipedia table'!A108</f>
         <v>Rappahannock</v>
       </c>
-      <c r="B105" s="3">
+      <c r="B115" s="3">
         <f>'Wikipedia table'!B108</f>
         <v>2231</v>
       </c>
-      <c r="C105" s="3">
+      <c r="C115" s="3">
         <f>'Wikipedia table'!D108</f>
         <v>1812</v>
       </c>
-      <c r="D105">
+      <c r="D115">
         <f>'Wikipedia table'!F108</f>
         <v>6</v>
       </c>
-      <c r="E105" s="3">
-        <f>SUM(B105:D105)</f>
+      <c r="E115" s="3">
+        <f>SUM(B115:D115)</f>
         <v>4049</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="15" t="str">
-        <f>'Wikipedia table'!A109</f>
-        <v>Richmond City</v>
-      </c>
-      <c r="B106" s="16">
-        <f>'Wikipedia table'!B109</f>
-        <v>11883</v>
-      </c>
-      <c r="C106" s="16">
-        <f>'Wikipedia table'!D109</f>
-        <v>79019</v>
-      </c>
-      <c r="D106" s="15">
-        <f>'Wikipedia table'!F109</f>
-        <v>212</v>
-      </c>
-      <c r="E106" s="16">
-        <f>SUM(B106:D106)</f>
-        <v>91114</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" t="str">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" t="str">
+        <f>'Wikipedia table'!A81</f>
+        <v>Manassas Park</v>
+      </c>
+      <c r="B116" s="3">
+        <f>'Wikipedia table'!B81</f>
+        <v>1151</v>
+      </c>
+      <c r="C116" s="3">
+        <f>'Wikipedia table'!D81</f>
+        <v>2852</v>
+      </c>
+      <c r="D116">
+        <f>'Wikipedia table'!F81</f>
+        <v>5</v>
+      </c>
+      <c r="E116" s="3">
+        <f>SUM(B116:D116)</f>
+        <v>4008</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" t="str">
+        <f>'Wikipedia table'!A82</f>
+        <v>Martinsville</v>
+      </c>
+      <c r="B117" s="3">
+        <f>'Wikipedia table'!B82</f>
+        <v>1451</v>
+      </c>
+      <c r="C117" s="3">
+        <f>'Wikipedia table'!D82</f>
+        <v>2534</v>
+      </c>
+      <c r="D117">
+        <f>'Wikipedia table'!F82</f>
+        <v>7</v>
+      </c>
+      <c r="E117" s="3">
+        <f>SUM(B117:D117)</f>
+        <v>3992</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" t="str">
+        <f>'Wikipedia table'!A126</f>
+        <v>Sussex</v>
+      </c>
+      <c r="B118" s="3">
+        <f>'Wikipedia table'!B126</f>
+        <v>1802</v>
+      </c>
+      <c r="C118" s="3">
+        <f>'Wikipedia table'!D126</f>
+        <v>2035</v>
+      </c>
+      <c r="D118">
+        <f>'Wikipedia table'!F126</f>
+        <v>4</v>
+      </c>
+      <c r="E118" s="3">
+        <f>SUM(B118:D118)</f>
+        <v>3841</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" t="str">
+        <f>'Wikipedia table'!A125</f>
+        <v>Surry</v>
+      </c>
+      <c r="B119" s="3">
+        <f>'Wikipedia table'!B125</f>
+        <v>1707</v>
+      </c>
+      <c r="C119" s="3">
+        <f>'Wikipedia table'!D125</f>
+        <v>1873</v>
+      </c>
+      <c r="D119">
+        <f>'Wikipedia table'!F125</f>
+        <v>4</v>
+      </c>
+      <c r="E119" s="3">
+        <f>SUM(B119:D119)</f>
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" t="str">
+        <f>'Wikipedia table'!A26</f>
+        <v>Charles City</v>
+      </c>
+      <c r="B120" s="3">
+        <f>'Wikipedia table'!B26</f>
+        <v>1485</v>
+      </c>
+      <c r="C120" s="3">
+        <f>'Wikipedia table'!D26</f>
+        <v>2002</v>
+      </c>
+      <c r="D120">
+        <f>'Wikipedia table'!F26</f>
+        <v>5</v>
+      </c>
+      <c r="E120" s="3">
+        <f>SUM(B120:D120)</f>
+        <v>3492</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" t="str">
+        <f>'Wikipedia table'!A58</f>
+        <v>Greensville</v>
+      </c>
+      <c r="B121" s="3">
+        <f>'Wikipedia table'!B58</f>
+        <v>1427</v>
+      </c>
+      <c r="C121" s="3">
+        <f>'Wikipedia table'!D58</f>
+        <v>1902</v>
+      </c>
+      <c r="D121">
+        <f>'Wikipedia table'!F58</f>
+        <v>8</v>
+      </c>
+      <c r="E121" s="3">
+        <f>SUM(B121:D121)</f>
+        <v>3337</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" t="str">
+        <f>'Wikipedia table'!A69</f>
+        <v>King and Queen</v>
+      </c>
+      <c r="B122" s="3">
+        <f>'Wikipedia table'!B69</f>
+        <v>1985</v>
+      </c>
+      <c r="C122" s="3">
+        <f>'Wikipedia table'!D69</f>
+        <v>1292</v>
+      </c>
+      <c r="D122">
+        <f>'Wikipedia table'!F69</f>
+        <v>4</v>
+      </c>
+      <c r="E122" s="3">
+        <f>SUM(B122:D122)</f>
+        <v>3281</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" t="str">
         <f>'Wikipedia table'!A110</f>
         <v>Richmond County</v>
       </c>
-      <c r="B107" s="3">
+      <c r="B123" s="3">
         <f>'Wikipedia table'!B110</f>
         <v>1997</v>
       </c>
-      <c r="C107" s="3">
+      <c r="C123" s="3">
         <f>'Wikipedia table'!D110</f>
         <v>1124</v>
       </c>
-      <c r="D107">
+      <c r="D123">
         <f>'Wikipedia table'!F110</f>
         <v>5</v>
       </c>
-      <c r="E107" s="3">
-        <f>SUM(B107:D107)</f>
-        <v>3126</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" t="str">
-        <f>'Wikipedia table'!A111</f>
-        <v>Roanoke City</v>
-      </c>
-      <c r="B108" s="3">
-        <f>'Wikipedia table'!B111</f>
-        <v>10153</v>
-      </c>
-      <c r="C108" s="3">
-        <f>'Wikipedia table'!D111</f>
-        <v>20700</v>
-      </c>
-      <c r="D108">
-        <f>'Wikipedia table'!F111</f>
-        <v>83</v>
-      </c>
-      <c r="E108" s="3">
-        <f>SUM(B108:D108)</f>
-        <v>30936</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="15" t="str">
-        <f>'Wikipedia table'!A112</f>
-        <v>Roanoke County</v>
-      </c>
-      <c r="B109" s="16">
-        <f>'Wikipedia table'!B112</f>
-        <v>24728</v>
-      </c>
-      <c r="C109" s="16">
-        <f>'Wikipedia table'!D112</f>
-        <v>18062</v>
-      </c>
-      <c r="D109" s="15">
-        <f>'Wikipedia table'!F112</f>
-        <v>97</v>
-      </c>
-      <c r="E109" s="16">
-        <f>SUM(B109:D109)</f>
-        <v>42887</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" t="str">
-        <f>'Wikipedia table'!A113</f>
-        <v>Rockbridge</v>
-      </c>
-      <c r="B110" s="3">
-        <f>'Wikipedia table'!B113</f>
-        <v>6599</v>
-      </c>
-      <c r="C110" s="3">
-        <f>'Wikipedia table'!D113</f>
-        <v>3557</v>
-      </c>
-      <c r="D110">
-        <f>'Wikipedia table'!F113</f>
-        <v>7</v>
-      </c>
-      <c r="E110" s="3">
-        <f>SUM(B110:D110)</f>
-        <v>10163</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" t="str">
-        <f>'Wikipedia table'!A114</f>
-        <v>Rockingham</v>
-      </c>
-      <c r="B111" s="3">
-        <f>'Wikipedia table'!B114</f>
-        <v>24498</v>
-      </c>
-      <c r="C111" s="3">
-        <f>'Wikipedia table'!D114</f>
-        <v>11622</v>
-      </c>
-      <c r="D111">
-        <f>'Wikipedia table'!F114</f>
-        <v>76</v>
-      </c>
-      <c r="E111" s="3">
-        <f>SUM(B111:D111)</f>
-        <v>36196</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" t="str">
-        <f>'Wikipedia table'!A115</f>
-        <v>Russell</v>
-      </c>
-      <c r="B112" s="3">
-        <f>'Wikipedia table'!B115</f>
-        <v>7268</v>
-      </c>
-      <c r="C112" s="3">
-        <f>'Wikipedia table'!D115</f>
-        <v>1673</v>
-      </c>
-      <c r="D112">
-        <f>'Wikipedia table'!F115</f>
-        <v>17</v>
-      </c>
-      <c r="E112" s="3">
-        <f>SUM(B112:D112)</f>
-        <v>8958</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" t="str">
-        <f>'Wikipedia table'!A116</f>
-        <v>Salem</v>
-      </c>
-      <c r="B113" s="3">
-        <f>'Wikipedia table'!B116</f>
-        <v>5282</v>
-      </c>
-      <c r="C113" s="3">
-        <f>'Wikipedia table'!D116</f>
-        <v>4150</v>
-      </c>
-      <c r="D113">
-        <f>'Wikipedia table'!F116</f>
-        <v>32</v>
-      </c>
-      <c r="E113" s="3">
-        <f>SUM(B113:D113)</f>
-        <v>9464</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="15" t="str">
-        <f>'Wikipedia table'!A117</f>
-        <v>Scott</v>
-      </c>
-      <c r="B114" s="16">
-        <f>'Wikipedia table'!B117</f>
-        <v>6103</v>
-      </c>
-      <c r="C114" s="16">
-        <f>'Wikipedia table'!D117</f>
-        <v>1235</v>
-      </c>
-      <c r="D114" s="15">
-        <f>'Wikipedia table'!F117</f>
-        <v>15</v>
-      </c>
-      <c r="E114" s="16">
-        <f>SUM(B114:D114)</f>
-        <v>7353</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" t="str">
-        <f>'Wikipedia table'!A118</f>
-        <v>Shenandoah</v>
-      </c>
-      <c r="B115" s="3">
-        <f>'Wikipedia table'!B118</f>
-        <v>12488</v>
-      </c>
-      <c r="C115" s="3">
-        <f>'Wikipedia table'!D118</f>
-        <v>5698</v>
-      </c>
-      <c r="D115">
-        <f>'Wikipedia table'!F118</f>
-        <v>37</v>
-      </c>
-      <c r="E115" s="3">
-        <f>SUM(B115:D115)</f>
-        <v>18223</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" t="str">
-        <f>'Wikipedia table'!A119</f>
-        <v>Smyth</v>
-      </c>
-      <c r="B116" s="3">
-        <f>'Wikipedia table'!B119</f>
-        <v>7712</v>
-      </c>
-      <c r="C116" s="3">
-        <f>'Wikipedia table'!D119</f>
-        <v>2298</v>
-      </c>
-      <c r="D116">
-        <f>'Wikipedia table'!F119</f>
-        <v>18</v>
-      </c>
-      <c r="E116" s="3">
-        <f>SUM(B116:D116)</f>
-        <v>10028</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" t="str">
-        <f>'Wikipedia table'!A120</f>
-        <v>Southampton</v>
-      </c>
-      <c r="B117" s="3">
-        <f>'Wikipedia table'!B120</f>
-        <v>4492</v>
-      </c>
-      <c r="C117" s="3">
-        <f>'Wikipedia table'!D120</f>
-        <v>2945</v>
-      </c>
-      <c r="D117">
-        <f>'Wikipedia table'!F120</f>
-        <v>8</v>
-      </c>
-      <c r="E117" s="3">
-        <f>SUM(B117:D117)</f>
-        <v>7445</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="15" t="str">
-        <f>'Wikipedia table'!A121</f>
-        <v>Spotsylvania</v>
-      </c>
-      <c r="B118" s="16">
-        <f>'Wikipedia table'!B121</f>
-        <v>29015</v>
-      </c>
-      <c r="C118" s="16">
-        <f>'Wikipedia table'!D121</f>
-        <v>30748</v>
-      </c>
-      <c r="D118" s="15">
-        <f>'Wikipedia table'!F121</f>
-        <v>104</v>
-      </c>
-      <c r="E118" s="16">
-        <f>SUM(B118:D118)</f>
-        <v>59867</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="15" t="str">
-        <f>'Wikipedia table'!A122</f>
-        <v>Stafford</v>
-      </c>
-      <c r="B119" s="16">
-        <f>'Wikipedia table'!B122</f>
-        <v>27774</v>
-      </c>
-      <c r="C119" s="16">
-        <f>'Wikipedia table'!D122</f>
-        <v>35327</v>
-      </c>
-      <c r="D119" s="15">
-        <f>'Wikipedia table'!F122</f>
-        <v>115</v>
-      </c>
-      <c r="E119" s="16">
-        <f>SUM(B119:D119)</f>
-        <v>63216</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" t="str">
-        <f>'Wikipedia table'!A123</f>
-        <v>Staunton</v>
-      </c>
-      <c r="B120" s="3">
-        <f>'Wikipedia table'!B123</f>
-        <v>4236</v>
-      </c>
-      <c r="C120" s="3">
-        <f>'Wikipedia table'!D123</f>
-        <v>6580</v>
-      </c>
-      <c r="D120">
-        <f>'Wikipedia table'!F123</f>
-        <v>18</v>
-      </c>
-      <c r="E120" s="3">
-        <f>SUM(B120:D120)</f>
-        <v>10834</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" t="str">
-        <f>'Wikipedia table'!A124</f>
-        <v>Suffolk</v>
-      </c>
-      <c r="B121" s="3">
-        <f>'Wikipedia table'!B124</f>
-        <v>15935</v>
-      </c>
-      <c r="C121" s="3">
-        <f>'Wikipedia table'!D124</f>
-        <v>25696</v>
-      </c>
-      <c r="D121">
-        <f>'Wikipedia table'!F124</f>
-        <v>80</v>
-      </c>
-      <c r="E121" s="3">
-        <f>SUM(B121:D121)</f>
-        <v>41711</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" t="str">
-        <f>'Wikipedia table'!A125</f>
-        <v>Surry</v>
-      </c>
-      <c r="B122" s="3">
-        <f>'Wikipedia table'!B125</f>
-        <v>1707</v>
-      </c>
-      <c r="C122" s="3">
-        <f>'Wikipedia table'!D125</f>
-        <v>1873</v>
-      </c>
-      <c r="D122">
-        <f>'Wikipedia table'!F125</f>
-        <v>4</v>
-      </c>
-      <c r="E122" s="3">
-        <f>SUM(B122:D122)</f>
-        <v>3584</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" t="str">
-        <f>'Wikipedia table'!A126</f>
-        <v>Sussex</v>
-      </c>
-      <c r="B123" s="3">
-        <f>'Wikipedia table'!B126</f>
-        <v>1802</v>
-      </c>
-      <c r="C123" s="3">
-        <f>'Wikipedia table'!D126</f>
-        <v>2035</v>
-      </c>
-      <c r="D123">
-        <f>'Wikipedia table'!F126</f>
-        <v>4</v>
-      </c>
       <c r="E123" s="3">
         <f>SUM(B123:D123)</f>
-        <v>3841</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="str">
-        <f>'Wikipedia table'!A127</f>
-        <v>Tazewell</v>
+        <f>'Wikipedia table'!A48</f>
+        <v>Franklin City</v>
       </c>
       <c r="B124" s="3">
-        <f>'Wikipedia table'!B127</f>
-        <v>10407</v>
+        <f>'Wikipedia table'!B48</f>
+        <v>1084</v>
       </c>
       <c r="C124" s="3">
-        <f>'Wikipedia table'!D127</f>
-        <v>2248</v>
+        <f>'Wikipedia table'!D48</f>
+        <v>1849</v>
       </c>
       <c r="D124">
-        <f>'Wikipedia table'!F127</f>
-        <v>21</v>
+        <f>'Wikipedia table'!F48</f>
+        <v>2</v>
       </c>
       <c r="E124" s="3">
         <f>SUM(B124:D124)</f>
-        <v>12676</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="15" t="str">
-        <f>'Wikipedia table'!A128</f>
-        <v>Virginia Beach</v>
-      </c>
-      <c r="B125" s="16">
-        <f>'Wikipedia table'!B128</f>
-        <v>75013</v>
-      </c>
-      <c r="C125" s="16">
-        <f>'Wikipedia table'!D128</f>
-        <v>94339</v>
-      </c>
-      <c r="D125" s="15">
-        <f>'Wikipedia table'!F128</f>
-        <v>269</v>
-      </c>
-      <c r="E125" s="16">
+        <v>2935</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" t="str">
+        <f>'Wikipedia table'!A16</f>
+        <v>Bland</v>
+      </c>
+      <c r="B125" s="3">
+        <f>'Wikipedia table'!B16</f>
+        <v>1974</v>
+      </c>
+      <c r="C125" s="3">
+        <f>'Wikipedia table'!D16</f>
+        <v>441</v>
+      </c>
+      <c r="D125">
+        <f>'Wikipedia table'!F16</f>
+        <v>3</v>
+      </c>
+      <c r="E125" s="3">
         <f>SUM(B125:D125)</f>
-        <v>169621</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="str">
-        <f>'Wikipedia table'!A129</f>
-        <v>Warren</v>
+        <f>'Wikipedia table'!A34</f>
+        <v>Craig</v>
       </c>
       <c r="B126" s="3">
-        <f>'Wikipedia table'!B129</f>
-        <v>10433</v>
+        <f>'Wikipedia table'!B34</f>
+        <v>1806</v>
       </c>
       <c r="C126" s="3">
-        <f>'Wikipedia table'!D129</f>
-        <v>5757</v>
+        <f>'Wikipedia table'!D34</f>
+        <v>467</v>
       </c>
       <c r="D126">
-        <f>'Wikipedia table'!F129</f>
-        <v>39</v>
+        <f>'Wikipedia table'!F34</f>
+        <v>6</v>
       </c>
       <c r="E126" s="3">
         <f>SUM(B126:D126)</f>
-        <v>16229</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="15" t="str">
-        <f>'Wikipedia table'!A130</f>
-        <v>Washington</v>
-      </c>
-      <c r="B127" s="16">
-        <f>'Wikipedia table'!B130</f>
-        <v>15614</v>
-      </c>
-      <c r="C127" s="16">
-        <f>'Wikipedia table'!D130</f>
-        <v>5382</v>
-      </c>
-      <c r="D127" s="15">
-        <f>'Wikipedia table'!F130</f>
-        <v>43</v>
-      </c>
-      <c r="E127" s="16">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" t="str">
+        <f>'Wikipedia table'!A74</f>
+        <v>Lexington</v>
+      </c>
+      <c r="B127" s="3">
+        <f>'Wikipedia table'!B74</f>
+        <v>686</v>
+      </c>
+      <c r="C127" s="3">
+        <f>'Wikipedia table'!D74</f>
+        <v>1475</v>
+      </c>
+      <c r="D127">
+        <f>'Wikipedia table'!F74</f>
+        <v>6</v>
+      </c>
+      <c r="E127" s="3">
         <f>SUM(B127:D127)</f>
-        <v>21039</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="str">
-        <f>'Wikipedia table'!A131</f>
-        <v>Waynesboro</v>
+        <f>'Wikipedia table'!A22</f>
+        <v>Buena Vista</v>
       </c>
       <c r="B128" s="3">
-        <f>'Wikipedia table'!B131</f>
-        <v>4037</v>
+        <f>'Wikipedia table'!B22</f>
+        <v>1392</v>
       </c>
       <c r="C128" s="3">
-        <f>'Wikipedia table'!D131</f>
-        <v>4459</v>
+        <f>'Wikipedia table'!D22</f>
+        <v>696</v>
       </c>
       <c r="D128">
-        <f>'Wikipedia table'!F131</f>
-        <v>11</v>
+        <f>'Wikipedia table'!F22</f>
+        <v>9</v>
       </c>
       <c r="E128" s="3">
         <f>SUM(B128:D128)</f>
-        <v>8507</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="str">
-        <f>'Wikipedia table'!A132</f>
-        <v>Westmoreland</v>
+        <f>'Wikipedia table'!A14</f>
+        <v>Bath</v>
       </c>
       <c r="B129" s="3">
-        <f>'Wikipedia table'!B132</f>
-        <v>4396</v>
+        <f>'Wikipedia table'!B14</f>
+        <v>1421</v>
       </c>
       <c r="C129" s="3">
-        <f>'Wikipedia table'!D132</f>
-        <v>3733</v>
+        <f>'Wikipedia table'!D14</f>
+        <v>493</v>
       </c>
       <c r="D129">
-        <f>'Wikipedia table'!F132</f>
-        <v>8</v>
+        <f>'Wikipedia table'!F14</f>
+        <v>5</v>
       </c>
       <c r="E129" s="3">
         <f>SUM(B129:D129)</f>
-        <v>8137</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="str">
-        <f>'Wikipedia table'!A133</f>
-        <v>Williamsburg</v>
+        <f>'Wikipedia table'!A52</f>
+        <v>Galax</v>
       </c>
       <c r="B130" s="3">
-        <f>'Wikipedia table'!B133</f>
-        <v>1647</v>
+        <f>'Wikipedia table'!B52</f>
+        <v>1284</v>
       </c>
       <c r="C130" s="3">
-        <f>'Wikipedia table'!D133</f>
-        <v>5063</v>
+        <f>'Wikipedia table'!D52</f>
+        <v>597</v>
       </c>
       <c r="D130">
-        <f>'Wikipedia table'!F133</f>
-        <v>9</v>
+        <f>'Wikipedia table'!F52</f>
+        <v>1</v>
       </c>
       <c r="E130" s="3">
         <f>SUM(B130:D130)</f>
-        <v>6719</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="str">
-        <f>'Wikipedia table'!A134</f>
-        <v>Winchester</v>
+        <f>'Wikipedia table'!A33</f>
+        <v>Covington</v>
       </c>
       <c r="B131" s="3">
-        <f>'Wikipedia table'!B134</f>
-        <v>3485</v>
+        <f>'Wikipedia table'!B33</f>
+        <v>999</v>
       </c>
       <c r="C131" s="3">
-        <f>'Wikipedia table'!D134</f>
-        <v>5318</v>
+        <f>'Wikipedia table'!D33</f>
+        <v>678</v>
       </c>
       <c r="D131">
-        <f>'Wikipedia table'!F134</f>
-        <v>16</v>
+        <f>'Wikipedia table'!F33</f>
+        <v>0</v>
       </c>
       <c r="E131" s="3">
         <f>SUM(B131:D131)</f>
-        <v>8819</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="str">
-        <f>'Wikipedia table'!A135</f>
-        <v>Wise</v>
+        <f>'Wikipedia table'!A40</f>
+        <v>Emporia</v>
       </c>
       <c r="B132" s="3">
-        <f>'Wikipedia table'!B135</f>
-        <v>8744</v>
+        <f>'Wikipedia table'!B40</f>
+        <v>544</v>
       </c>
       <c r="C132" s="3">
-        <f>'Wikipedia table'!D135</f>
-        <v>2281</v>
+        <f>'Wikipedia table'!D40</f>
+        <v>1119</v>
       </c>
       <c r="D132">
-        <f>'Wikipedia table'!F135</f>
-        <v>22</v>
+        <f>'Wikipedia table'!F40</f>
+        <v>3</v>
       </c>
       <c r="E132" s="3">
         <f>SUM(B132:D132)</f>
-        <v>11047</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="str">
-        <f>'Wikipedia table'!A136</f>
-        <v>Wythe</v>
+        <f>'Wikipedia table'!A65</f>
+        <v>Highland</v>
       </c>
       <c r="B133" s="3">
-        <f>'Wikipedia table'!B136</f>
-        <v>8426</v>
+        <f>'Wikipedia table'!B65</f>
+        <v>831</v>
       </c>
       <c r="C133" s="3">
-        <f>'Wikipedia table'!D136</f>
-        <v>2594</v>
+        <f>'Wikipedia table'!D65</f>
+        <v>362</v>
       </c>
       <c r="D133">
-        <f>'Wikipedia table'!F136</f>
-        <v>24</v>
+        <f>'Wikipedia table'!F65</f>
+        <v>1</v>
       </c>
       <c r="E133" s="3">
         <f>SUM(B133:D133)</f>
-        <v>11044</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="str">
-        <f>'Wikipedia table'!A137</f>
-        <v>York</v>
+        <f>'Wikipedia table'!A93</f>
+        <v>Norton</v>
       </c>
       <c r="B134" s="3">
-        <f>'Wikipedia table'!B137</f>
-        <v>15684</v>
+        <f>'Wikipedia table'!B93</f>
+        <v>721</v>
       </c>
       <c r="C134" s="3">
-        <f>'Wikipedia table'!D137</f>
-        <v>15769</v>
+        <f>'Wikipedia table'!D93</f>
+        <v>332</v>
       </c>
       <c r="D134">
-        <f>'Wikipedia table'!F137</f>
-        <v>47</v>
+        <f>'Wikipedia table'!F93</f>
+        <v>2</v>
       </c>
       <c r="E134" s="3">
         <f>SUM(B134:D134)</f>
-        <v>31500</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
     </row>
-    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
     </row>
-    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
     </row>
-    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
     </row>
-    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
     </row>
-    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
     </row>
-    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
     </row>
-    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
     </row>
-    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
     </row>
-    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
     </row>
-    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
     </row>
-    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
     </row>
-    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
     </row>
-    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
     </row>
-    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
     </row>
-    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
     </row>
-    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
     </row>
-    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
     </row>
-    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
     </row>
-    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
     </row>
-    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
     </row>
-    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
     </row>
-    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
     </row>
-    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
     </row>
-    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
     </row>
-    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
     </row>
-    <row r="170" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
     </row>
-    <row r="171" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
     </row>
-    <row r="172" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
     </row>
-    <row r="173" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
     </row>
-    <row r="174" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
     </row>
-    <row r="175" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
     </row>
-    <row r="176" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
     </row>
-    <row r="177" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
     </row>
-    <row r="178" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
     </row>
-    <row r="179" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
     </row>
-    <row r="180" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
     </row>
-    <row r="181" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
     </row>
-    <row r="182" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
     </row>
-    <row r="183" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
     </row>
-    <row r="184" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
     </row>
-    <row r="185" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
     </row>
-    <row r="186" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
     </row>
-    <row r="187" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
     </row>
-    <row r="188" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
     </row>
-    <row r="189" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
     </row>
-    <row r="190" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
     </row>
-    <row r="191" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
     </row>
-    <row r="192" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
     </row>
-    <row r="193" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
     </row>
-    <row r="194" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
     </row>
-    <row r="195" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
     </row>
-    <row r="196" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
     </row>
-    <row r="197" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
     </row>
-    <row r="198" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
     </row>
-    <row r="199" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
     </row>
-    <row r="200" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
     </row>
-    <row r="201" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
     </row>
-    <row r="202" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
     </row>
-    <row r="203" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
     </row>
-    <row r="204" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
     </row>
-    <row r="205" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
     </row>
-    <row r="206" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E134">
-    <sortCondition ref="A2:A134"/>
+    <sortCondition descending="1" ref="E2:E134"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -5092,14 +4652,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A78A6D-9BEE-4D40-8307-8FE775F578D9}">
   <dimension ref="A1:J138"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="15.125" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
@@ -5110,7 +4670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
@@ -5124,7 +4684,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="13"/>
       <c r="H3" s="14" t="s">
         <v>7</v>
@@ -5133,7 +4693,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -5158,7 +4718,7 @@
       <c r="H4" s="14"/>
       <c r="J4" s="14"/>
     </row>
-    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -5190,7 +4750,7 @@
         <v>13064</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -5222,7 +4782,7 @@
         <v>55895</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -5254,7 +4814,7 @@
         <v>62844</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -5286,7 +4846,7 @@
         <v>5801</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -5318,7 +4878,7 @@
         <v>6360</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -5350,7 +4910,7 @@
         <v>13125</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
@@ -5382,7 +4942,7 @@
         <v>7386</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>28</v>
       </c>
@@ -5414,7 +4974,7 @@
         <v>99821</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
@@ -5446,7 +5006,7 @@
         <v>34194</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -5478,7 +5038,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>35</v>
       </c>
@@ -5510,7 +5070,7 @@
         <v>39271</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>38</v>
       </c>
@@ -5542,7 +5102,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>41</v>
       </c>
@@ -5574,7 +5134,7 @@
         <v>16821</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>44</v>
       </c>
@@ -5606,7 +5166,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>47</v>
       </c>
@@ -5638,7 +5198,7 @@
         <v>5934</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>48</v>
       </c>
@@ -5670,7 +5230,7 @@
         <v>5413</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>51</v>
       </c>
@@ -5702,7 +5262,7 @@
         <v>6055</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>54</v>
       </c>
@@ -5734,7 +5294,7 @@
         <v>2097</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>57</v>
       </c>
@@ -5766,7 +5326,7 @@
         <v>23042</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>60</v>
       </c>
@@ -5798,7 +5358,7 @@
         <v>13436</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>61</v>
       </c>
@@ -5830,7 +5390,7 @@
         <v>11348</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>64</v>
       </c>
@@ -5862,7 +5422,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>65</v>
       </c>
@@ -5894,7 +5454,7 @@
         <v>4710</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>68</v>
       </c>
@@ -5926,7 +5486,7 @@
         <v>18890</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>69</v>
       </c>
@@ -5958,7 +5518,7 @@
         <v>96282</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>70</v>
       </c>
@@ -5990,7 +5550,7 @@
         <v>170910</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>71</v>
       </c>
@@ -6022,7 +5582,7 @@
         <v>7629</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>74</v>
       </c>
@@ -6054,7 +5614,7 @@
         <v>6587</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>77</v>
       </c>
@@ -6086,7 +5646,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>80</v>
       </c>
@@ -6118,7 +5678,7 @@
         <v>2279</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>83</v>
       </c>
@@ -6150,7 +5710,7 @@
         <v>21839</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>86</v>
       </c>
@@ -6182,7 +5742,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>89</v>
       </c>
@@ -6214,7 +5774,7 @@
         <v>12299</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>90</v>
       </c>
@@ -6246,7 +5806,7 @@
         <v>4462</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>93</v>
       </c>
@@ -6278,7 +5838,7 @@
         <v>12078</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>96</v>
       </c>
@@ -6310,7 +5870,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>97</v>
       </c>
@@ -6342,7 +5902,7 @@
         <v>4869</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>100</v>
       </c>
@@ -6374,7 +5934,7 @@
         <v>10435</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>101</v>
       </c>
@@ -6406,7 +5966,7 @@
         <v>447252</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>102</v>
       </c>
@@ -6438,7 +5998,7 @@
         <v>7600</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>103</v>
       </c>
@@ -6470,7 +6030,7 @@
         <v>34566</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>106</v>
       </c>
@@ -6502,7 +6062,7 @@
         <v>7425</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>109</v>
       </c>
@@ -6534,7 +6094,7 @@
         <v>13449</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>112</v>
       </c>
@@ -6566,7 +6126,7 @@
         <v>2935</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>113</v>
       </c>
@@ -6598,7 +6158,7 @@
         <v>23189</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>116</v>
       </c>
@@ -6630,7 +6190,7 @@
         <v>38990</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>119</v>
       </c>
@@ -6662,7 +6222,7 @@
         <v>10537</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>120</v>
       </c>
@@ -6694,7 +6254,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>123</v>
       </c>
@@ -6726,7 +6286,7 @@
         <v>6781</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>126</v>
       </c>
@@ -6758,7 +6318,7 @@
         <v>17341</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>129</v>
       </c>
@@ -6790,7 +6350,7 @@
         <v>17089</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>132</v>
       </c>
@@ -6822,7 +6382,7 @@
         <v>5889</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>134</v>
       </c>
@@ -6854,7 +6414,7 @@
         <v>9510</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>137</v>
       </c>
@@ -6886,7 +6446,7 @@
         <v>3337</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>138</v>
       </c>
@@ -6918,7 +6478,7 @@
         <v>13321</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>141</v>
       </c>
@@ -6950,7 +6510,7 @@
         <v>47323</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>142</v>
       </c>
@@ -6982,7 +6542,7 @@
         <v>60367</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>145</v>
       </c>
@@ -7014,7 +6574,7 @@
         <v>13189</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>146</v>
       </c>
@@ -7046,7 +6606,7 @@
         <v>149446</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>147</v>
       </c>
@@ -7078,7 +6638,7 @@
         <v>17500</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>150</v>
       </c>
@@ -7110,7 +6670,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>153</v>
       </c>
@@ -7142,7 +6702,7 @@
         <v>6675</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>154</v>
       </c>
@@ -7174,7 +6734,7 @@
         <v>19195</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>157</v>
       </c>
@@ -7206,7 +6766,7 @@
         <v>42695</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>158</v>
       </c>
@@ -7238,7 +6798,7 @@
         <v>3281</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>161</v>
       </c>
@@ -7270,7 +6830,7 @@
         <v>11645</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>164</v>
       </c>
@@ -7302,7 +6862,7 @@
         <v>9064</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>167</v>
       </c>
@@ -7334,7 +6894,7 @@
         <v>6030</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>170</v>
       </c>
@@ -7366,7 +6926,7 @@
         <v>6465</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>173</v>
       </c>
@@ -7398,7 +6958,7 @@
         <v>2167</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>174</v>
       </c>
@@ -7430,7 +6990,7 @@
         <v>168316</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>175</v>
       </c>
@@ -7462,7 +7022,7 @@
         <v>18951</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>178</v>
       </c>
@@ -7494,7 +7054,7 @@
         <v>4499</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>181</v>
       </c>
@@ -7526,7 +7086,7 @@
         <v>26795</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>184</v>
       </c>
@@ -7558,7 +7118,7 @@
         <v>6654</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>187</v>
       </c>
@@ -7590,7 +7150,7 @@
         <v>11725</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>188</v>
       </c>
@@ -7622,7 +7182,7 @@
         <v>4008</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>189</v>
       </c>
@@ -7654,7 +7214,7 @@
         <v>3992</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>190</v>
       </c>
@@ -7686,7 +7246,7 @@
         <v>4802</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>193</v>
       </c>
@@ -7718,7 +7278,7 @@
         <v>11819</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>196</v>
       </c>
@@ -7750,7 +7310,7 @@
         <v>5653</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>199</v>
       </c>
@@ -7782,7 +7342,7 @@
         <v>36732</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>200</v>
       </c>
@@ -7814,7 +7374,7 @@
         <v>7725</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>201</v>
       </c>
@@ -7846,7 +7406,7 @@
         <v>13913</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>204</v>
       </c>
@@ -7878,7 +7438,7 @@
         <v>56489</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>205</v>
       </c>
@@ -7910,7 +7470,7 @@
         <v>64219</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>206</v>
       </c>
@@ -7942,7 +7502,7 @@
         <v>5537</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>207</v>
       </c>
@@ -7974,7 +7534,7 @@
         <v>6833</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>210</v>
       </c>
@@ -8006,7 +7566,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>213</v>
       </c>
@@ -8038,7 +7598,7 @@
         <v>5391</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>216</v>
       </c>
@@ -8070,7 +7630,7 @@
         <v>17332</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>219</v>
       </c>
@@ -8102,7 +7662,7 @@
         <v>9329</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>222</v>
       </c>
@@ -8134,7 +7694,7 @@
         <v>6612</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>225</v>
       </c>
@@ -8166,7 +7726,7 @@
         <v>9960</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>226</v>
       </c>
@@ -8198,7 +7758,7 @@
         <v>24749</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>229</v>
       </c>
@@ -8230,7 +7790,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>232</v>
       </c>
@@ -8262,7 +7822,7 @@
         <v>31453</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>233</v>
       </c>
@@ -8294,7 +7854,7 @@
         <v>17051</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>236</v>
       </c>
@@ -8326,7 +7886,7 @@
         <v>7455</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>237</v>
       </c>
@@ -8358,7 +7918,7 @@
         <v>13706</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>240</v>
       </c>
@@ -8390,7 +7950,7 @@
         <v>165888</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>241</v>
       </c>
@@ -8422,7 +7982,7 @@
         <v>12556</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>244</v>
       </c>
@@ -8454,7 +8014,7 @@
         <v>4693</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>245</v>
       </c>
@@ -8486,7 +8046,7 @@
         <v>4049</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
         <v>248</v>
       </c>
@@ -8518,7 +8078,7 @@
         <v>91114</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>249</v>
       </c>
@@ -8550,7 +8110,7 @@
         <v>3126</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>252</v>
       </c>
@@ -8582,7 +8142,7 @@
         <v>30936</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>253</v>
       </c>
@@ -8614,7 +8174,7 @@
         <v>42887</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>256</v>
       </c>
@@ -8646,7 +8206,7 @@
         <v>10163</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>259</v>
       </c>
@@ -8678,7 +8238,7 @@
         <v>36196</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>262</v>
       </c>
@@ -8710,7 +8270,7 @@
         <v>8958</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>265</v>
       </c>
@@ -8742,7 +8302,7 @@
         <v>9464</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>268</v>
       </c>
@@ -8774,7 +8334,7 @@
         <v>7353</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>271</v>
       </c>
@@ -8806,7 +8366,7 @@
         <v>18223</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>274</v>
       </c>
@@ -8838,7 +8398,7 @@
         <v>10028</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>277</v>
       </c>
@@ -8870,7 +8430,7 @@
         <v>7445</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>280</v>
       </c>
@@ -8902,7 +8462,7 @@
         <v>59867</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>281</v>
       </c>
@@ -8934,7 +8494,7 @@
         <v>63216</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
         <v>282</v>
       </c>
@@ -8966,7 +8526,7 @@
         <v>10834</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>283</v>
       </c>
@@ -8998,7 +8558,7 @@
         <v>41711</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
         <v>284</v>
       </c>
@@ -9030,7 +8590,7 @@
         <v>3584</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>285</v>
       </c>
@@ -9062,7 +8622,7 @@
         <v>3841</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>286</v>
       </c>
@@ -9094,7 +8654,7 @@
         <v>12676</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>289</v>
       </c>
@@ -9126,7 +8686,7 @@
         <v>169621</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
         <v>290</v>
       </c>
@@ -9158,7 +8718,7 @@
         <v>16229</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>293</v>
       </c>
@@ -9190,7 +8750,7 @@
         <v>21039</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>296</v>
       </c>
@@ -9222,7 +8782,7 @@
         <v>8507</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>297</v>
       </c>
@@ -9254,7 +8814,7 @@
         <v>8137</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>300</v>
       </c>
@@ -9286,7 +8846,7 @@
         <v>6719</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>301</v>
       </c>
@@ -9318,7 +8878,7 @@
         <v>8819</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>302</v>
       </c>
@@ -9350,7 +8910,7 @@
         <v>11047</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>305</v>
       </c>
@@ -9382,7 +8942,7 @@
         <v>11044</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>308</v>
       </c>
@@ -9414,7 +8974,7 @@
         <v>31500</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
         <v>309</v>
       </c>
